--- a/api/clv3/xlsx/en/OrganisationRegistrationAgency.xlsx
+++ b/api/clv3/xlsx/en/OrganisationRegistrationAgency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3391" uniqueCount="2248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3403" uniqueCount="2256">
   <si>
     <t>code</t>
   </si>
@@ -1435,6 +1435,18 @@
     <t>https://gov-id-finder.codeforiati.org/countries/CO/</t>
   </si>
   <si>
+    <t>CO-CUIN</t>
+  </si>
+  <si>
+    <t>Colombian Unique Institutional Code</t>
+  </si>
+  <si>
+    <t>The Código Único Institucional (CUIN) is a 15-digit numeric code assigned to Colombian public sector entities by the Contaduría General de la Nación (CGN — National Accounting Authority). It was adopted by Resolution No. 767 of 2013 and has applied to all entities comprising the Colombian public sector from 1 January 2014. The CUIN classifies entities across three top-level sectors: Public non-financial corporations; Public financial corporations; General government The CUIN is an 8-part mnemonic code encoding sector, subsector, entity type, supra-region, and territorial level. It is used for public finance monitoring and reporting, and is mandatory for all public sector entities registered in the CHIP (Consolidador de Hacienda e Información Pública) system. It is also required by DIAN for annual exogenous information reporting by public entities. The CUIN is distinct from the NIT (tax identification number) and applies exclusively to public sector entities.</t>
+  </si>
+  <si>
+    <t>https://www.contaduria.gov.co/definicion-del-codigo-cuin</t>
+  </si>
+  <si>
     <t>CO-NIT</t>
   </si>
   <si>
@@ -2651,6 +2663,18 @@
   </si>
   <si>
     <t>https://gov-id-finder.codeforiati.org/countries/GW/</t>
+  </si>
+  <si>
+    <t>GW-NIF</t>
+  </si>
+  <si>
+    <t>Guinea-Bissau Tax Identification Number</t>
+  </si>
+  <si>
+    <t>The Número de Identificação Fiscal (NIF) is issued by the Direção-Geral das Contribuições e Impostos (DGCI), under the Ministry of Finance of Guinea-Bissau. It identifies taxpayers, including organisations, in the DGCI's fiscal database. NIF identifiers can be used to uniquely identify organisations in open data publications.</t>
+  </si>
+  <si>
+    <t>https://kontaktu.mef.gw/</t>
   </si>
   <si>
     <t>GY-COA</t>
@@ -7102,7 +7126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G567"/>
+  <dimension ref="A1:G569"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -9902,7 +9926,7 @@
         <v>12</v>
       </c>
       <c r="G122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -9925,7 +9949,7 @@
         <v>12</v>
       </c>
       <c r="G123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -9936,10 +9960,10 @@
         <v>482</v>
       </c>
       <c r="C124" t="s">
-        <v>9</v>
+        <v>483</v>
       </c>
       <c r="D124" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>484</v>
@@ -9959,10 +9983,10 @@
         <v>486</v>
       </c>
       <c r="C125" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" t="s">
         <v>487</v>
-      </c>
-      <c r="D125" t="s">
-        <v>483</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>488</v>
@@ -9971,7 +9995,7 @@
         <v>12</v>
       </c>
       <c r="G125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -9982,10 +10006,10 @@
         <v>490</v>
       </c>
       <c r="C126" t="s">
-        <v>9</v>
+        <v>491</v>
       </c>
       <c r="D126" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>492</v>
@@ -9994,7 +10018,7 @@
         <v>12</v>
       </c>
       <c r="G126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -10097,10 +10121,10 @@
         <v>510</v>
       </c>
       <c r="C131" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" t="s">
         <v>511</v>
-      </c>
-      <c r="D131" t="s">
-        <v>507</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>512</v>
@@ -10109,7 +10133,7 @@
         <v>12</v>
       </c>
       <c r="G131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -10120,10 +10144,10 @@
         <v>514</v>
       </c>
       <c r="C132" t="s">
-        <v>9</v>
+        <v>515</v>
       </c>
       <c r="D132" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>516</v>
@@ -10132,7 +10156,7 @@
         <v>12</v>
       </c>
       <c r="G132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -10143,10 +10167,10 @@
         <v>518</v>
       </c>
       <c r="C133" t="s">
+        <v>9</v>
+      </c>
+      <c r="D133" t="s">
         <v>519</v>
-      </c>
-      <c r="D133" t="s">
-        <v>515</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>520</v>
@@ -10155,7 +10179,7 @@
         <v>12</v>
       </c>
       <c r="G133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -10169,7 +10193,7 @@
         <v>523</v>
       </c>
       <c r="D134" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>524</v>
@@ -10178,7 +10202,7 @@
         <v>12</v>
       </c>
       <c r="G134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -10189,10 +10213,10 @@
         <v>526</v>
       </c>
       <c r="C135" t="s">
-        <v>9</v>
+        <v>527</v>
       </c>
       <c r="D135" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>528</v>
@@ -10212,10 +10236,10 @@
         <v>530</v>
       </c>
       <c r="C136" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" t="s">
         <v>531</v>
-      </c>
-      <c r="D136" t="s">
-        <v>527</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>532</v>
@@ -10224,7 +10248,7 @@
         <v>12</v>
       </c>
       <c r="G136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -10235,10 +10259,10 @@
         <v>534</v>
       </c>
       <c r="C137" t="s">
-        <v>9</v>
+        <v>535</v>
       </c>
       <c r="D137" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>536</v>
@@ -10247,7 +10271,7 @@
         <v>12</v>
       </c>
       <c r="G137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -10281,10 +10305,10 @@
         <v>542</v>
       </c>
       <c r="C139" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" t="s">
         <v>543</v>
-      </c>
-      <c r="D139" t="s">
-        <v>539</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>544</v>
@@ -10304,10 +10328,10 @@
         <v>546</v>
       </c>
       <c r="C140" t="s">
-        <v>9</v>
+        <v>547</v>
       </c>
       <c r="D140" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>548</v>
@@ -10396,10 +10420,10 @@
         <v>562</v>
       </c>
       <c r="C144" t="s">
+        <v>9</v>
+      </c>
+      <c r="D144" t="s">
         <v>563</v>
-      </c>
-      <c r="D144" t="s">
-        <v>559</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>564</v>
@@ -10408,7 +10432,7 @@
         <v>12</v>
       </c>
       <c r="G144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -10419,10 +10443,10 @@
         <v>566</v>
       </c>
       <c r="C145" t="s">
-        <v>9</v>
+        <v>567</v>
       </c>
       <c r="D145" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>568</v>
@@ -10431,7 +10455,7 @@
         <v>12</v>
       </c>
       <c r="G145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -10442,10 +10466,10 @@
         <v>570</v>
       </c>
       <c r="C146" t="s">
+        <v>9</v>
+      </c>
+      <c r="D146" t="s">
         <v>571</v>
-      </c>
-      <c r="D146" t="s">
-        <v>567</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>572</v>
@@ -10454,7 +10478,7 @@
         <v>12</v>
       </c>
       <c r="G146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -10468,33 +10492,33 @@
         <v>575</v>
       </c>
       <c r="D147" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F147" t="s">
         <v>12</v>
       </c>
       <c r="G147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
+        <v>577</v>
+      </c>
+      <c r="B148" t="s">
+        <v>578</v>
+      </c>
+      <c r="C148" t="s">
+        <v>579</v>
+      </c>
+      <c r="D148" t="s">
+        <v>571</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="B148" t="s">
-        <v>577</v>
-      </c>
-      <c r="C148" t="s">
-        <v>9</v>
-      </c>
-      <c r="D148" t="s">
-        <v>578</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>579</v>
       </c>
       <c r="F148" t="s">
         <v>12</v>
@@ -10511,10 +10535,10 @@
         <v>581</v>
       </c>
       <c r="C149" t="s">
+        <v>9</v>
+      </c>
+      <c r="D149" t="s">
         <v>582</v>
-      </c>
-      <c r="D149" t="s">
-        <v>578</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>583</v>
@@ -10523,7 +10547,7 @@
         <v>12</v>
       </c>
       <c r="G149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -10537,7 +10561,7 @@
         <v>586</v>
       </c>
       <c r="D150" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>587</v>
@@ -10546,7 +10570,7 @@
         <v>12</v>
       </c>
       <c r="G150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -10557,10 +10581,10 @@
         <v>589</v>
       </c>
       <c r="C151" t="s">
-        <v>9</v>
+        <v>590</v>
       </c>
       <c r="D151" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>591</v>
@@ -10626,10 +10650,10 @@
         <v>601</v>
       </c>
       <c r="C154" t="s">
+        <v>9</v>
+      </c>
+      <c r="D154" t="s">
         <v>602</v>
-      </c>
-      <c r="D154" t="s">
-        <v>598</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>603</v>
@@ -10652,7 +10676,7 @@
         <v>606</v>
       </c>
       <c r="D155" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>607</v>
@@ -10661,7 +10685,7 @@
         <v>12</v>
       </c>
       <c r="G155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -10669,36 +10693,36 @@
         <v>608</v>
       </c>
       <c r="B156" t="s">
-        <v>282</v>
+        <v>609</v>
       </c>
       <c r="C156" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D156" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F156" t="s">
         <v>12</v>
       </c>
       <c r="G156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B157" t="s">
-        <v>612</v>
+        <v>282</v>
       </c>
       <c r="C157" t="s">
         <v>613</v>
       </c>
       <c r="D157" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>614</v>
@@ -10707,7 +10731,7 @@
         <v>12</v>
       </c>
       <c r="G157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -10718,10 +10742,10 @@
         <v>616</v>
       </c>
       <c r="C158" t="s">
-        <v>9</v>
+        <v>617</v>
       </c>
       <c r="D158" t="s">
-        <v>617</v>
+        <v>602</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>618</v>
@@ -10741,10 +10765,10 @@
         <v>620</v>
       </c>
       <c r="C159" t="s">
+        <v>9</v>
+      </c>
+      <c r="D159" t="s">
         <v>621</v>
-      </c>
-      <c r="D159" t="s">
-        <v>617</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>622</v>
@@ -10753,7 +10777,7 @@
         <v>12</v>
       </c>
       <c r="G159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -10767,7 +10791,7 @@
         <v>625</v>
       </c>
       <c r="D160" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>626</v>
@@ -10790,7 +10814,7 @@
         <v>629</v>
       </c>
       <c r="D161" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>630</v>
@@ -10813,7 +10837,7 @@
         <v>633</v>
       </c>
       <c r="D162" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>634</v>
@@ -10822,7 +10846,7 @@
         <v>12</v>
       </c>
       <c r="G162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -10833,10 +10857,10 @@
         <v>636</v>
       </c>
       <c r="C163" t="s">
-        <v>9</v>
+        <v>637</v>
       </c>
       <c r="D163" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>638</v>
@@ -10845,7 +10869,7 @@
         <v>12</v>
       </c>
       <c r="G163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -10856,10 +10880,10 @@
         <v>640</v>
       </c>
       <c r="C164" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" t="s">
         <v>641</v>
-      </c>
-      <c r="D164" t="s">
-        <v>637</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>642</v>
@@ -10868,7 +10892,7 @@
         <v>12</v>
       </c>
       <c r="G164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -10882,7 +10906,7 @@
         <v>645</v>
       </c>
       <c r="D165" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>646</v>
@@ -10902,10 +10926,10 @@
         <v>648</v>
       </c>
       <c r="C166" t="s">
-        <v>9</v>
+        <v>649</v>
       </c>
       <c r="D166" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>650</v>
@@ -10914,7 +10938,7 @@
         <v>12</v>
       </c>
       <c r="G166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -11017,16 +11041,16 @@
         <v>668</v>
       </c>
       <c r="C171" t="s">
+        <v>9</v>
+      </c>
+      <c r="D171" t="s">
         <v>669</v>
-      </c>
-      <c r="D171" t="s">
-        <v>665</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>670</v>
       </c>
       <c r="F171" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G171" t="b">
         <v>0</v>
@@ -11043,16 +11067,16 @@
         <v>673</v>
       </c>
       <c r="D172" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>674</v>
       </c>
       <c r="F172" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -11063,10 +11087,10 @@
         <v>676</v>
       </c>
       <c r="C173" t="s">
-        <v>9</v>
+        <v>677</v>
       </c>
       <c r="D173" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>678</v>
@@ -11075,7 +11099,7 @@
         <v>12</v>
       </c>
       <c r="G173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -11086,33 +11110,33 @@
         <v>680</v>
       </c>
       <c r="C174" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" t="s">
         <v>681</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="E174" s="1" t="s">
-        <v>683</v>
-      </c>
       <c r="F174" t="s">
         <v>12</v>
       </c>
       <c r="G174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
+        <v>683</v>
+      </c>
+      <c r="B175" t="s">
         <v>684</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
         <v>685</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D175" t="s">
         <v>686</v>
-      </c>
-      <c r="D175" t="s">
-        <v>682</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>687</v>
@@ -11132,33 +11156,33 @@
         <v>689</v>
       </c>
       <c r="C176" t="s">
-        <v>9</v>
+        <v>690</v>
       </c>
       <c r="D176" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F176" t="s">
         <v>12</v>
       </c>
       <c r="G176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B177" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C177" t="s">
-        <v>693</v>
+        <v>9</v>
       </c>
       <c r="D177" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>694</v>
@@ -11167,7 +11191,7 @@
         <v>12</v>
       </c>
       <c r="G177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -11181,7 +11205,7 @@
         <v>697</v>
       </c>
       <c r="D178" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>698</v>
@@ -11204,7 +11228,7 @@
         <v>701</v>
       </c>
       <c r="D179" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>702</v>
@@ -11227,7 +11251,7 @@
         <v>705</v>
       </c>
       <c r="D180" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>706</v>
@@ -11250,16 +11274,16 @@
         <v>709</v>
       </c>
       <c r="D181" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>710</v>
       </c>
       <c r="F181" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -11273,13 +11297,13 @@
         <v>713</v>
       </c>
       <c r="D182" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F182" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G182" t="b">
         <v>0</v>
@@ -11296,16 +11320,16 @@
         <v>717</v>
       </c>
       <c r="D183" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>718</v>
       </c>
       <c r="F183" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -11319,7 +11343,7 @@
         <v>721</v>
       </c>
       <c r="D184" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>722</v>
@@ -11342,7 +11366,7 @@
         <v>725</v>
       </c>
       <c r="D185" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>726</v>
@@ -11365,7 +11389,7 @@
         <v>729</v>
       </c>
       <c r="D186" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>730</v>
@@ -11388,7 +11412,7 @@
         <v>733</v>
       </c>
       <c r="D187" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>734</v>
@@ -11411,7 +11435,7 @@
         <v>737</v>
       </c>
       <c r="D188" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>738</v>
@@ -11434,7 +11458,7 @@
         <v>741</v>
       </c>
       <c r="D189" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>742</v>
@@ -11457,7 +11481,7 @@
         <v>745</v>
       </c>
       <c r="D190" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>746</v>
@@ -11480,7 +11504,7 @@
         <v>749</v>
       </c>
       <c r="D191" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>750</v>
@@ -11503,7 +11527,7 @@
         <v>753</v>
       </c>
       <c r="D192" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>754</v>
@@ -11512,7 +11536,7 @@
         <v>12</v>
       </c>
       <c r="G192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -11526,7 +11550,7 @@
         <v>757</v>
       </c>
       <c r="D193" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>758</v>
@@ -11549,7 +11573,7 @@
         <v>761</v>
       </c>
       <c r="D194" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>762</v>
@@ -11558,7 +11582,7 @@
         <v>12</v>
       </c>
       <c r="G194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -11572,7 +11596,7 @@
         <v>765</v>
       </c>
       <c r="D195" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>766</v>
@@ -11595,7 +11619,7 @@
         <v>769</v>
       </c>
       <c r="D196" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>770</v>
@@ -11618,7 +11642,7 @@
         <v>773</v>
       </c>
       <c r="D197" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>774</v>
@@ -11627,7 +11651,7 @@
         <v>12</v>
       </c>
       <c r="G197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -11641,7 +11665,7 @@
         <v>777</v>
       </c>
       <c r="D198" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>778</v>
@@ -11650,7 +11674,7 @@
         <v>12</v>
       </c>
       <c r="G198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -11661,10 +11685,10 @@
         <v>780</v>
       </c>
       <c r="C199" t="s">
-        <v>9</v>
+        <v>781</v>
       </c>
       <c r="D199" t="s">
-        <v>781</v>
+        <v>686</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>782</v>
@@ -11673,7 +11697,7 @@
         <v>12</v>
       </c>
       <c r="G199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -11707,10 +11731,10 @@
         <v>788</v>
       </c>
       <c r="C201" t="s">
+        <v>9</v>
+      </c>
+      <c r="D201" t="s">
         <v>789</v>
-      </c>
-      <c r="D201" t="s">
-        <v>785</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>790</v>
@@ -11733,7 +11757,7 @@
         <v>793</v>
       </c>
       <c r="D202" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>794</v>
@@ -11742,7 +11766,7 @@
         <v>12</v>
       </c>
       <c r="G202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -11753,10 +11777,10 @@
         <v>796</v>
       </c>
       <c r="C203" t="s">
-        <v>9</v>
+        <v>797</v>
       </c>
       <c r="D203" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>798</v>
@@ -11765,7 +11789,7 @@
         <v>12</v>
       </c>
       <c r="G203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -11799,10 +11823,10 @@
         <v>804</v>
       </c>
       <c r="C205" t="s">
+        <v>9</v>
+      </c>
+      <c r="D205" t="s">
         <v>805</v>
-      </c>
-      <c r="D205" t="s">
-        <v>801</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>806</v>
@@ -11822,10 +11846,10 @@
         <v>808</v>
       </c>
       <c r="C206" t="s">
-        <v>9</v>
+        <v>809</v>
       </c>
       <c r="D206" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>810</v>
@@ -11834,7 +11858,7 @@
         <v>12</v>
       </c>
       <c r="G206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -11845,10 +11869,10 @@
         <v>812</v>
       </c>
       <c r="C207" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" t="s">
         <v>813</v>
-      </c>
-      <c r="D207" t="s">
-        <v>809</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>814</v>
@@ -11857,7 +11881,7 @@
         <v>12</v>
       </c>
       <c r="G207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -11871,7 +11895,7 @@
         <v>817</v>
       </c>
       <c r="D208" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>818</v>
@@ -11880,7 +11904,7 @@
         <v>12</v>
       </c>
       <c r="G208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -11894,7 +11918,7 @@
         <v>821</v>
       </c>
       <c r="D209" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>822</v>
@@ -11903,7 +11927,7 @@
         <v>12</v>
       </c>
       <c r="G209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -11914,10 +11938,10 @@
         <v>824</v>
       </c>
       <c r="C210" t="s">
-        <v>9</v>
+        <v>825</v>
       </c>
       <c r="D210" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>826</v>
@@ -11972,7 +11996,7 @@
         <v>12</v>
       </c>
       <c r="G212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -12018,7 +12042,7 @@
         <v>12</v>
       </c>
       <c r="G214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -12041,7 +12065,7 @@
         <v>12</v>
       </c>
       <c r="G215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -12064,7 +12088,7 @@
         <v>12</v>
       </c>
       <c r="G216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -12098,56 +12122,56 @@
         <v>856</v>
       </c>
       <c r="C218" t="s">
+        <v>9</v>
+      </c>
+      <c r="D218" t="s">
         <v>857</v>
       </c>
-      <c r="D218" t="s">
+      <c r="E218" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="E218" s="1" t="s">
-        <v>859</v>
-      </c>
       <c r="F218" t="s">
         <v>12</v>
       </c>
       <c r="G218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
+        <v>859</v>
+      </c>
+      <c r="B219" t="s">
         <v>860</v>
       </c>
-      <c r="B219" t="s">
+      <c r="C219" t="s">
         <v>861</v>
       </c>
-      <c r="C219" t="s">
-        <v>9</v>
-      </c>
       <c r="D219" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F219" t="s">
         <v>12</v>
       </c>
       <c r="G219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B220" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C220" t="s">
-        <v>865</v>
+        <v>9</v>
       </c>
       <c r="D220" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>866</v>
@@ -12156,7 +12180,7 @@
         <v>12</v>
       </c>
       <c r="G220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -12170,7 +12194,7 @@
         <v>869</v>
       </c>
       <c r="D221" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>870</v>
@@ -12190,10 +12214,10 @@
         <v>872</v>
       </c>
       <c r="C222" t="s">
-        <v>9</v>
+        <v>873</v>
       </c>
       <c r="D222" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>874</v>
@@ -12202,7 +12226,7 @@
         <v>12</v>
       </c>
       <c r="G222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -12225,7 +12249,7 @@
         <v>12</v>
       </c>
       <c r="G223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -12248,7 +12272,7 @@
         <v>12</v>
       </c>
       <c r="G224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -12259,10 +12283,10 @@
         <v>884</v>
       </c>
       <c r="C225" t="s">
-        <v>9</v>
+        <v>885</v>
       </c>
       <c r="D225" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>886</v>
@@ -12282,10 +12306,10 @@
         <v>888</v>
       </c>
       <c r="C226" t="s">
+        <v>9</v>
+      </c>
+      <c r="D226" t="s">
         <v>889</v>
-      </c>
-      <c r="D226" t="s">
-        <v>885</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>890</v>
@@ -12294,7 +12318,7 @@
         <v>12</v>
       </c>
       <c r="G226" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -12328,10 +12352,10 @@
         <v>896</v>
       </c>
       <c r="C228" t="s">
-        <v>9</v>
+        <v>897</v>
       </c>
       <c r="D228" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>898</v>
@@ -12340,7 +12364,7 @@
         <v>12</v>
       </c>
       <c r="G228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -12351,10 +12375,10 @@
         <v>900</v>
       </c>
       <c r="C229" t="s">
+        <v>9</v>
+      </c>
+      <c r="D229" t="s">
         <v>901</v>
-      </c>
-      <c r="D229" t="s">
-        <v>897</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>902</v>
@@ -12363,7 +12387,7 @@
         <v>12</v>
       </c>
       <c r="G229" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -12420,10 +12444,10 @@
         <v>912</v>
       </c>
       <c r="C232" t="s">
+        <v>9</v>
+      </c>
+      <c r="D232" t="s">
         <v>913</v>
-      </c>
-      <c r="D232" t="s">
-        <v>905</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>914</v>
@@ -12432,7 +12456,7 @@
         <v>12</v>
       </c>
       <c r="G232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -12443,10 +12467,10 @@
         <v>916</v>
       </c>
       <c r="C233" t="s">
-        <v>9</v>
+        <v>917</v>
       </c>
       <c r="D233" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>918</v>
@@ -12469,10 +12493,10 @@
         <v>921</v>
       </c>
       <c r="D234" t="s">
+        <v>913</v>
+      </c>
+      <c r="E234" s="1" t="s">
         <v>922</v>
-      </c>
-      <c r="E234" s="1" t="s">
-        <v>923</v>
       </c>
       <c r="F234" t="s">
         <v>12</v>
@@ -12483,16 +12507,16 @@
     </row>
     <row r="235" spans="1:7">
       <c r="A235" t="s">
+        <v>923</v>
+      </c>
+      <c r="B235" t="s">
         <v>924</v>
       </c>
-      <c r="B235" t="s">
+      <c r="C235" t="s">
+        <v>9</v>
+      </c>
+      <c r="D235" t="s">
         <v>925</v>
-      </c>
-      <c r="C235" t="s">
-        <v>9</v>
-      </c>
-      <c r="D235" t="s">
-        <v>922</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>926</v>
@@ -12501,7 +12525,7 @@
         <v>12</v>
       </c>
       <c r="G235" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -12512,13 +12536,13 @@
         <v>928</v>
       </c>
       <c r="C236" t="s">
-        <v>9</v>
+        <v>929</v>
       </c>
       <c r="D236" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F236" t="s">
         <v>12</v>
@@ -12529,16 +12553,16 @@
     </row>
     <row r="237" spans="1:7">
       <c r="A237" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B237" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C237" t="s">
-        <v>933</v>
+        <v>9</v>
       </c>
       <c r="D237" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>934</v>
@@ -12558,19 +12582,19 @@
         <v>936</v>
       </c>
       <c r="C238" t="s">
+        <v>9</v>
+      </c>
+      <c r="D238" t="s">
         <v>937</v>
-      </c>
-      <c r="D238" t="s">
-        <v>929</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>938</v>
       </c>
       <c r="F238" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G238" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -12584,7 +12608,7 @@
         <v>941</v>
       </c>
       <c r="D239" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>942</v>
@@ -12607,13 +12631,13 @@
         <v>945</v>
       </c>
       <c r="D240" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>946</v>
       </c>
       <c r="F240" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G240" t="b">
         <v>0</v>
@@ -12630,13 +12654,13 @@
         <v>949</v>
       </c>
       <c r="D241" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>950</v>
       </c>
       <c r="F241" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G241" t="b">
         <v>0</v>
@@ -12653,7 +12677,7 @@
         <v>953</v>
       </c>
       <c r="D242" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>954</v>
@@ -12676,13 +12700,13 @@
         <v>957</v>
       </c>
       <c r="D243" t="s">
+        <v>937</v>
+      </c>
+      <c r="E243" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="E243" s="1" t="s">
-        <v>959</v>
-      </c>
       <c r="F243" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G243" t="b">
         <v>0</v>
@@ -12690,16 +12714,16 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
+        <v>959</v>
+      </c>
+      <c r="B244" t="s">
         <v>960</v>
       </c>
-      <c r="B244" t="s">
+      <c r="C244" t="s">
         <v>961</v>
       </c>
-      <c r="C244" t="s">
-        <v>9</v>
-      </c>
       <c r="D244" t="s">
-        <v>958</v>
+        <v>937</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>962</v>
@@ -12722,10 +12746,10 @@
         <v>965</v>
       </c>
       <c r="D245" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F245" t="s">
         <v>12</v>
@@ -12736,16 +12760,16 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B246" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C246" t="s">
         <v>9</v>
       </c>
       <c r="D246" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>970</v>
@@ -12768,7 +12792,7 @@
         <v>973</v>
       </c>
       <c r="D247" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>974</v>
@@ -12777,7 +12801,7 @@
         <v>12</v>
       </c>
       <c r="G247" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -12788,10 +12812,10 @@
         <v>976</v>
       </c>
       <c r="C248" t="s">
+        <v>9</v>
+      </c>
+      <c r="D248" t="s">
         <v>977</v>
-      </c>
-      <c r="D248" t="s">
-        <v>969</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>978</v>
@@ -12800,7 +12824,7 @@
         <v>12</v>
       </c>
       <c r="G248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -12811,10 +12835,10 @@
         <v>980</v>
       </c>
       <c r="C249" t="s">
-        <v>9</v>
+        <v>981</v>
       </c>
       <c r="D249" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>982</v>
@@ -12823,7 +12847,7 @@
         <v>12</v>
       </c>
       <c r="G249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -12837,7 +12861,7 @@
         <v>985</v>
       </c>
       <c r="D250" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>986</v>
@@ -12846,7 +12870,7 @@
         <v>12</v>
       </c>
       <c r="G250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -12857,10 +12881,10 @@
         <v>988</v>
       </c>
       <c r="C251" t="s">
+        <v>9</v>
+      </c>
+      <c r="D251" t="s">
         <v>989</v>
-      </c>
-      <c r="D251" t="s">
-        <v>981</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>990</v>
@@ -12869,7 +12893,7 @@
         <v>12</v>
       </c>
       <c r="G251" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -12880,10 +12904,10 @@
         <v>992</v>
       </c>
       <c r="C252" t="s">
-        <v>9</v>
+        <v>993</v>
       </c>
       <c r="D252" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>994</v>
@@ -12906,7 +12930,7 @@
         <v>997</v>
       </c>
       <c r="D253" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>998</v>
@@ -12926,10 +12950,10 @@
         <v>1000</v>
       </c>
       <c r="C254" t="s">
+        <v>9</v>
+      </c>
+      <c r="D254" t="s">
         <v>1001</v>
-      </c>
-      <c r="D254" t="s">
-        <v>993</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>1002</v>
@@ -12952,7 +12976,7 @@
         <v>1005</v>
       </c>
       <c r="D255" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>1006</v>
@@ -12961,7 +12985,7 @@
         <v>12</v>
       </c>
       <c r="G255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -12972,10 +12996,10 @@
         <v>1008</v>
       </c>
       <c r="C256" t="s">
-        <v>9</v>
+        <v>1009</v>
       </c>
       <c r="D256" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>1010</v>
@@ -12995,10 +13019,10 @@
         <v>1012</v>
       </c>
       <c r="C257" t="s">
-        <v>9</v>
+        <v>1013</v>
       </c>
       <c r="D257" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>1014</v>
@@ -13018,10 +13042,10 @@
         <v>1016</v>
       </c>
       <c r="C258" t="s">
+        <v>9</v>
+      </c>
+      <c r="D258" t="s">
         <v>1017</v>
-      </c>
-      <c r="D258" t="s">
-        <v>1013</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>1018</v>
@@ -13030,7 +13054,7 @@
         <v>12</v>
       </c>
       <c r="G258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -13041,10 +13065,10 @@
         <v>1020</v>
       </c>
       <c r="C259" t="s">
+        <v>9</v>
+      </c>
+      <c r="D259" t="s">
         <v>1021</v>
-      </c>
-      <c r="D259" t="s">
-        <v>1013</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>1022</v>
@@ -13064,10 +13088,10 @@
         <v>1024</v>
       </c>
       <c r="C260" t="s">
-        <v>9</v>
+        <v>1025</v>
       </c>
       <c r="D260" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>1026</v>
@@ -13076,7 +13100,7 @@
         <v>12</v>
       </c>
       <c r="G260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -13087,10 +13111,10 @@
         <v>1028</v>
       </c>
       <c r="C261" t="s">
-        <v>9</v>
+        <v>1029</v>
       </c>
       <c r="D261" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>1030</v>
@@ -13110,10 +13134,10 @@
         <v>1032</v>
       </c>
       <c r="C262" t="s">
+        <v>9</v>
+      </c>
+      <c r="D262" t="s">
         <v>1033</v>
-      </c>
-      <c r="D262" t="s">
-        <v>1029</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>1034</v>
@@ -13122,7 +13146,7 @@
         <v>12</v>
       </c>
       <c r="G262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -13133,33 +13157,33 @@
         <v>1036</v>
       </c>
       <c r="C263" t="s">
+        <v>9</v>
+      </c>
+      <c r="D263" t="s">
         <v>1037</v>
       </c>
-      <c r="D263" t="s">
+      <c r="E263" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="E263" s="1" t="s">
-        <v>1039</v>
-      </c>
       <c r="F263" t="s">
         <v>12</v>
       </c>
       <c r="G263" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:7">
       <c r="A264" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B264" t="s">
         <v>1040</v>
       </c>
-      <c r="B264" t="s">
+      <c r="C264" t="s">
         <v>1041</v>
       </c>
-      <c r="C264" t="s">
-        <v>9</v>
-      </c>
       <c r="D264" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>1042</v>
@@ -13168,7 +13192,7 @@
         <v>12</v>
       </c>
       <c r="G264" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -13182,10 +13206,10 @@
         <v>1045</v>
       </c>
       <c r="D265" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
@@ -13196,71 +13220,71 @@
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B266" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C266" t="s">
-        <v>1049</v>
+        <v>9</v>
       </c>
       <c r="D266" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>1039</v>
+        <v>1050</v>
       </c>
       <c r="F266" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G266" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B267" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C267" t="s">
-        <v>9</v>
+        <v>1053</v>
       </c>
       <c r="D267" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F267" t="s">
         <v>12</v>
       </c>
       <c r="G267" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B268" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C268" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D268" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>1057</v>
+        <v>1047</v>
       </c>
       <c r="F268" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -13271,10 +13295,10 @@
         <v>1059</v>
       </c>
       <c r="C269" t="s">
+        <v>9</v>
+      </c>
+      <c r="D269" t="s">
         <v>1060</v>
-      </c>
-      <c r="D269" t="s">
-        <v>1052</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>1061</v>
@@ -13283,7 +13307,7 @@
         <v>12</v>
       </c>
       <c r="G269" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -13297,13 +13321,13 @@
         <v>1064</v>
       </c>
       <c r="D270" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>1065</v>
       </c>
       <c r="F270" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G270" t="b">
         <v>0</v>
@@ -13317,10 +13341,10 @@
         <v>1067</v>
       </c>
       <c r="C271" t="s">
-        <v>9</v>
+        <v>1068</v>
       </c>
       <c r="D271" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>1069</v>
@@ -13343,30 +13367,30 @@
         <v>1072</v>
       </c>
       <c r="D272" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E272" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="E272" s="1" t="s">
-        <v>1074</v>
-      </c>
       <c r="F272" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G272" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B273" t="s">
         <v>1075</v>
       </c>
-      <c r="B273" t="s">
+      <c r="C273" t="s">
+        <v>9</v>
+      </c>
+      <c r="D273" t="s">
         <v>1076</v>
-      </c>
-      <c r="C273" t="s">
-        <v>9</v>
-      </c>
-      <c r="D273" t="s">
-        <v>1073</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>1077</v>
@@ -13389,10 +13413,10 @@
         <v>1080</v>
       </c>
       <c r="D274" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F274" t="s">
         <v>12</v>
@@ -13403,16 +13427,16 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B275" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C275" t="s">
         <v>9</v>
       </c>
       <c r="D275" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>1085</v>
@@ -13421,7 +13445,7 @@
         <v>12</v>
       </c>
       <c r="G275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -13435,7 +13459,7 @@
         <v>1088</v>
       </c>
       <c r="D276" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>1089</v>
@@ -13467,7 +13491,7 @@
         <v>12</v>
       </c>
       <c r="G277" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -13490,7 +13514,7 @@
         <v>12</v>
       </c>
       <c r="G278" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -13501,10 +13525,10 @@
         <v>1099</v>
       </c>
       <c r="C279" t="s">
+        <v>9</v>
+      </c>
+      <c r="D279" t="s">
         <v>1100</v>
-      </c>
-      <c r="D279" t="s">
-        <v>1092</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>1101</v>
@@ -13513,7 +13537,7 @@
         <v>12</v>
       </c>
       <c r="G279" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -13527,7 +13551,7 @@
         <v>1104</v>
       </c>
       <c r="D280" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>1105</v>
@@ -13550,13 +13574,13 @@
         <v>1108</v>
       </c>
       <c r="D281" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="F281" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G281" t="b">
         <v>0</v>
@@ -13564,19 +13588,19 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B282" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C282" t="s">
-        <v>9</v>
+        <v>1112</v>
       </c>
       <c r="D282" t="s">
-        <v>1111</v>
+        <v>1100</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F282" t="s">
         <v>12</v>
@@ -13587,25 +13611,25 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B283" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C283" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E283" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="B283" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C283" t="s">
-        <v>1115</v>
-      </c>
-      <c r="D283" t="s">
-        <v>1111</v>
-      </c>
-      <c r="E283" s="1" t="s">
-        <v>1116</v>
-      </c>
       <c r="F283" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G283" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -13616,10 +13640,10 @@
         <v>1118</v>
       </c>
       <c r="C284" t="s">
+        <v>9</v>
+      </c>
+      <c r="D284" t="s">
         <v>1119</v>
-      </c>
-      <c r="D284" t="s">
-        <v>1111</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>1120</v>
@@ -13628,7 +13652,7 @@
         <v>12</v>
       </c>
       <c r="G284" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -13642,7 +13666,7 @@
         <v>1123</v>
       </c>
       <c r="D285" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>1124</v>
@@ -13665,10 +13689,10 @@
         <v>1127</v>
       </c>
       <c r="D286" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="F286" t="s">
         <v>12</v>
@@ -13679,42 +13703,42 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B287" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C287" t="s">
-        <v>9</v>
+        <v>1131</v>
       </c>
       <c r="D287" t="s">
-        <v>1130</v>
+        <v>1119</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="F287" t="s">
         <v>12</v>
       </c>
       <c r="G287" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B288" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C288" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D288" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E288" s="1" t="s">
         <v>1132</v>
-      </c>
-      <c r="B288" t="s">
-        <v>624</v>
-      </c>
-      <c r="C288" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D288" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E288" s="1" t="s">
-        <v>1134</v>
       </c>
       <c r="F288" t="s">
         <v>12</v>
@@ -13725,19 +13749,19 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B289" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C289" t="s">
-        <v>1137</v>
+        <v>9</v>
       </c>
       <c r="D289" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="F289" t="s">
         <v>12</v>
@@ -13748,16 +13772,16 @@
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B290" t="s">
-        <v>1140</v>
+        <v>628</v>
       </c>
       <c r="C290" t="s">
         <v>1141</v>
       </c>
       <c r="D290" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>1142</v>
@@ -13766,7 +13790,7 @@
         <v>12</v>
       </c>
       <c r="G290" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -13777,10 +13801,10 @@
         <v>1144</v>
       </c>
       <c r="C291" t="s">
-        <v>9</v>
+        <v>1145</v>
       </c>
       <c r="D291" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>1146</v>
@@ -13789,7 +13813,7 @@
         <v>12</v>
       </c>
       <c r="G291" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -13800,10 +13824,10 @@
         <v>1148</v>
       </c>
       <c r="C292" t="s">
-        <v>9</v>
+        <v>1149</v>
       </c>
       <c r="D292" t="s">
-        <v>1149</v>
+        <v>1138</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>1150</v>
@@ -13869,13 +13893,13 @@
         <v>1160</v>
       </c>
       <c r="C295" t="s">
+        <v>9</v>
+      </c>
+      <c r="D295" t="s">
         <v>1161</v>
       </c>
-      <c r="D295" t="s">
+      <c r="E295" s="1" t="s">
         <v>1162</v>
-      </c>
-      <c r="E295" s="1" t="s">
-        <v>1163</v>
       </c>
       <c r="F295" t="s">
         <v>12</v>
@@ -13886,16 +13910,16 @@
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B296" t="s">
         <v>1164</v>
       </c>
-      <c r="B296" t="s">
+      <c r="C296" t="s">
+        <v>9</v>
+      </c>
+      <c r="D296" t="s">
         <v>1165</v>
-      </c>
-      <c r="C296" t="s">
-        <v>9</v>
-      </c>
-      <c r="D296" t="s">
-        <v>1162</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>1166</v>
@@ -13915,33 +13939,33 @@
         <v>1168</v>
       </c>
       <c r="C297" t="s">
-        <v>9</v>
+        <v>1169</v>
       </c>
       <c r="D297" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="F297" t="s">
         <v>12</v>
       </c>
       <c r="G297" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B298" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C298" t="s">
         <v>9</v>
       </c>
       <c r="D298" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>1174</v>
@@ -13961,33 +13985,33 @@
         <v>1176</v>
       </c>
       <c r="C299" t="s">
+        <v>9</v>
+      </c>
+      <c r="D299" t="s">
         <v>1177</v>
       </c>
-      <c r="D299" t="s">
+      <c r="E299" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="E299" s="1" t="s">
-        <v>1179</v>
-      </c>
       <c r="F299" t="s">
         <v>12</v>
       </c>
       <c r="G299" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B300" t="s">
         <v>1180</v>
       </c>
-      <c r="B300" t="s">
+      <c r="C300" t="s">
+        <v>9</v>
+      </c>
+      <c r="D300" t="s">
         <v>1181</v>
-      </c>
-      <c r="C300" t="s">
-        <v>9</v>
-      </c>
-      <c r="D300" t="s">
-        <v>1178</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>1182</v>
@@ -14007,13 +14031,13 @@
         <v>1184</v>
       </c>
       <c r="C301" t="s">
-        <v>9</v>
+        <v>1185</v>
       </c>
       <c r="D301" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="F301" t="s">
         <v>12</v>
@@ -14024,16 +14048,16 @@
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B302" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C302" t="s">
         <v>9</v>
       </c>
       <c r="D302" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>1190</v>
@@ -14053,10 +14077,10 @@
         <v>1192</v>
       </c>
       <c r="C303" t="s">
+        <v>9</v>
+      </c>
+      <c r="D303" t="s">
         <v>1193</v>
-      </c>
-      <c r="D303" t="s">
-        <v>1189</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>1194</v>
@@ -14076,10 +14100,10 @@
         <v>1196</v>
       </c>
       <c r="C304" t="s">
+        <v>9</v>
+      </c>
+      <c r="D304" t="s">
         <v>1197</v>
-      </c>
-      <c r="D304" t="s">
-        <v>1189</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>1198</v>
@@ -14099,10 +14123,10 @@
         <v>1200</v>
       </c>
       <c r="C305" t="s">
-        <v>9</v>
+        <v>1201</v>
       </c>
       <c r="D305" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>1202</v>
@@ -14111,7 +14135,7 @@
         <v>12</v>
       </c>
       <c r="G305" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -14122,10 +14146,10 @@
         <v>1204</v>
       </c>
       <c r="C306" t="s">
-        <v>9</v>
+        <v>1205</v>
       </c>
       <c r="D306" t="s">
-        <v>1205</v>
+        <v>1197</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>1206</v>
@@ -14168,10 +14192,10 @@
         <v>1212</v>
       </c>
       <c r="C308" t="s">
+        <v>9</v>
+      </c>
+      <c r="D308" t="s">
         <v>1213</v>
-      </c>
-      <c r="D308" t="s">
-        <v>1209</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>1214</v>
@@ -14180,7 +14204,7 @@
         <v>12</v>
       </c>
       <c r="G308" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -14191,10 +14215,10 @@
         <v>1216</v>
       </c>
       <c r="C309" t="s">
+        <v>9</v>
+      </c>
+      <c r="D309" t="s">
         <v>1217</v>
-      </c>
-      <c r="D309" t="s">
-        <v>1209</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>1218</v>
@@ -14203,7 +14227,7 @@
         <v>12</v>
       </c>
       <c r="G309" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -14214,10 +14238,10 @@
         <v>1220</v>
       </c>
       <c r="C310" t="s">
-        <v>9</v>
+        <v>1221</v>
       </c>
       <c r="D310" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>1222</v>
@@ -14240,7 +14264,7 @@
         <v>1225</v>
       </c>
       <c r="D311" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>1226</v>
@@ -14249,7 +14273,7 @@
         <v>12</v>
       </c>
       <c r="G311" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -14306,19 +14330,19 @@
         <v>1236</v>
       </c>
       <c r="C314" t="s">
+        <v>9</v>
+      </c>
+      <c r="D314" t="s">
         <v>1237</v>
-      </c>
-      <c r="D314" t="s">
-        <v>1229</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>1238</v>
       </c>
       <c r="F314" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G314" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -14332,7 +14356,10 @@
         <v>1241</v>
       </c>
       <c r="D315" t="s">
-        <v>1229</v>
+        <v>1237</v>
+      </c>
+      <c r="E315" s="1" t="s">
+        <v>1242</v>
       </c>
       <c r="F315" t="s">
         <v>12</v>
@@ -14343,22 +14370,22 @@
     </row>
     <row r="316" spans="1:7">
       <c r="A316" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B316" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C316" t="s">
-        <v>9</v>
+        <v>1245</v>
       </c>
       <c r="D316" t="s">
-        <v>1244</v>
+        <v>1237</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="F316" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G316" t="b">
         <v>0</v>
@@ -14366,25 +14393,22 @@
     </row>
     <row r="317" spans="1:7">
       <c r="A317" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B317" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C317" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D317" t="s">
-        <v>1244</v>
-      </c>
-      <c r="E317" s="1" t="s">
-        <v>1249</v>
+        <v>1237</v>
       </c>
       <c r="F317" t="s">
         <v>12</v>
       </c>
       <c r="G317" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -14395,10 +14419,10 @@
         <v>1251</v>
       </c>
       <c r="C318" t="s">
+        <v>9</v>
+      </c>
+      <c r="D318" t="s">
         <v>1252</v>
-      </c>
-      <c r="D318" t="s">
-        <v>1244</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>1253</v>
@@ -14407,7 +14431,7 @@
         <v>12</v>
       </c>
       <c r="G318" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -14418,10 +14442,10 @@
         <v>1255</v>
       </c>
       <c r="C319" t="s">
-        <v>9</v>
+        <v>1256</v>
       </c>
       <c r="D319" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>1257</v>
@@ -14430,7 +14454,7 @@
         <v>12</v>
       </c>
       <c r="G319" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -14444,7 +14468,7 @@
         <v>1260</v>
       </c>
       <c r="D320" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>1261</v>
@@ -14533,10 +14557,10 @@
         <v>1275</v>
       </c>
       <c r="C324" t="s">
-        <v>9</v>
+        <v>1276</v>
       </c>
       <c r="D324" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>1277</v>
@@ -14579,10 +14603,10 @@
         <v>1283</v>
       </c>
       <c r="C326" t="s">
+        <v>9</v>
+      </c>
+      <c r="D326" t="s">
         <v>1284</v>
-      </c>
-      <c r="D326" t="s">
-        <v>1280</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>1285</v>
@@ -14683,7 +14707,7 @@
         <v>12</v>
       </c>
       <c r="G330" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:7">
@@ -14717,10 +14741,10 @@
         <v>1307</v>
       </c>
       <c r="C332" t="s">
-        <v>9</v>
+        <v>1308</v>
       </c>
       <c r="D332" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>1309</v>
@@ -14729,7 +14753,7 @@
         <v>12</v>
       </c>
       <c r="G332" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:7">
@@ -14740,10 +14764,10 @@
         <v>1311</v>
       </c>
       <c r="C333" t="s">
+        <v>9</v>
+      </c>
+      <c r="D333" t="s">
         <v>1312</v>
-      </c>
-      <c r="D333" t="s">
-        <v>1308</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>1313</v>
@@ -14775,7 +14799,7 @@
         <v>12</v>
       </c>
       <c r="G334" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:7">
@@ -14786,10 +14810,10 @@
         <v>1319</v>
       </c>
       <c r="C335" t="s">
-        <v>9</v>
+        <v>1320</v>
       </c>
       <c r="D335" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>1321</v>
@@ -14809,13 +14833,13 @@
         <v>1323</v>
       </c>
       <c r="C336" t="s">
+        <v>9</v>
+      </c>
+      <c r="D336" t="s">
         <v>1324</v>
       </c>
-      <c r="D336" t="s">
+      <c r="E336" s="1" t="s">
         <v>1325</v>
-      </c>
-      <c r="E336" s="1" t="s">
-        <v>1326</v>
       </c>
       <c r="F336" t="s">
         <v>12</v>
@@ -14826,16 +14850,16 @@
     </row>
     <row r="337" spans="1:7">
       <c r="A337" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B337" t="s">
         <v>1327</v>
       </c>
-      <c r="B337" t="s">
+      <c r="C337" t="s">
+        <v>9</v>
+      </c>
+      <c r="D337" t="s">
         <v>1328</v>
-      </c>
-      <c r="C337" t="s">
-        <v>9</v>
-      </c>
-      <c r="D337" t="s">
-        <v>1325</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>1329</v>
@@ -14844,7 +14868,7 @@
         <v>12</v>
       </c>
       <c r="G337" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:7">
@@ -14858,10 +14882,10 @@
         <v>1332</v>
       </c>
       <c r="D338" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="F338" t="s">
         <v>12</v>
@@ -14872,62 +14896,65 @@
     </row>
     <row r="339" spans="1:7">
       <c r="A339" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B339" t="s">
-        <v>282</v>
+        <v>1336</v>
       </c>
       <c r="C339" t="s">
-        <v>1335</v>
+        <v>9</v>
       </c>
       <c r="D339" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="F339" t="s">
         <v>12</v>
       </c>
       <c r="G339" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340" spans="1:7">
       <c r="A340" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B340" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C340" t="s">
-        <v>9</v>
+        <v>1340</v>
       </c>
       <c r="D340" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="F340" t="s">
         <v>12</v>
       </c>
       <c r="G340" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:7">
       <c r="A341" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B341" t="s">
-        <v>1342</v>
+        <v>282</v>
       </c>
       <c r="C341" t="s">
         <v>1343</v>
       </c>
       <c r="D341" t="s">
-        <v>1339</v>
+        <v>1333</v>
+      </c>
+      <c r="E341" s="1" t="s">
+        <v>1344</v>
       </c>
       <c r="F341" t="s">
         <v>12</v>
@@ -14938,42 +14965,39 @@
     </row>
     <row r="342" spans="1:7">
       <c r="A342" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B342" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="C342" t="s">
         <v>9</v>
       </c>
       <c r="D342" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="F342" t="s">
         <v>12</v>
       </c>
       <c r="G342" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343" spans="1:7">
       <c r="A343" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B343" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="C343" t="s">
-        <v>9</v>
+        <v>1351</v>
       </c>
       <c r="D343" t="s">
-        <v>1350</v>
-      </c>
-      <c r="E343" s="1" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="F343" t="s">
         <v>12</v>
@@ -15048,7 +15072,7 @@
         <v>12</v>
       </c>
       <c r="G346" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:7">
@@ -15094,7 +15118,7 @@
         <v>12</v>
       </c>
       <c r="G348" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349" spans="1:7">
@@ -15128,10 +15152,10 @@
         <v>1377</v>
       </c>
       <c r="C350" t="s">
+        <v>9</v>
+      </c>
+      <c r="D350" t="s">
         <v>1378</v>
-      </c>
-      <c r="D350" t="s">
-        <v>1374</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>1379</v>
@@ -15140,7 +15164,7 @@
         <v>12</v>
       </c>
       <c r="G350" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:7">
@@ -15177,30 +15201,30 @@
         <v>1386</v>
       </c>
       <c r="D352" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E352" s="1" t="s">
         <v>1387</v>
       </c>
-      <c r="E352" s="1" t="s">
-        <v>1388</v>
-      </c>
       <c r="F352" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G352" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353" spans="1:7">
       <c r="A353" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B353" t="s">
         <v>1389</v>
       </c>
-      <c r="B353" t="s">
+      <c r="C353" t="s">
+        <v>9</v>
+      </c>
+      <c r="D353" t="s">
         <v>1390</v>
-      </c>
-      <c r="C353" t="s">
-        <v>9</v>
-      </c>
-      <c r="D353" t="s">
-        <v>1387</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>1391</v>
@@ -15209,7 +15233,7 @@
         <v>12</v>
       </c>
       <c r="G353" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:7">
@@ -15223,10 +15247,10 @@
         <v>1394</v>
       </c>
       <c r="D354" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="F354" t="s">
         <v>165</v>
@@ -15237,16 +15261,16 @@
     </row>
     <row r="355" spans="1:7">
       <c r="A355" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B355" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="C355" t="s">
-        <v>1398</v>
+        <v>9</v>
       </c>
       <c r="D355" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>1399</v>
@@ -15255,7 +15279,7 @@
         <v>12</v>
       </c>
       <c r="G355" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356" spans="1:7">
@@ -15269,13 +15293,13 @@
         <v>1402</v>
       </c>
       <c r="D356" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>1403</v>
       </c>
       <c r="F356" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G356" t="b">
         <v>0</v>
@@ -15292,30 +15316,30 @@
         <v>1406</v>
       </c>
       <c r="D357" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E357" s="1" t="s">
         <v>1407</v>
       </c>
-      <c r="E357" s="1" t="s">
-        <v>1408</v>
-      </c>
       <c r="F357" t="s">
         <v>12</v>
       </c>
       <c r="G357" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:7">
       <c r="A358" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B358" t="s">
         <v>1409</v>
       </c>
-      <c r="B358" t="s">
+      <c r="C358" t="s">
         <v>1410</v>
       </c>
-      <c r="C358" t="s">
-        <v>9</v>
-      </c>
       <c r="D358" t="s">
-        <v>1407</v>
+        <v>1395</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>1411</v>
@@ -15338,10 +15362,10 @@
         <v>1414</v>
       </c>
       <c r="D359" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="F359" t="s">
         <v>12</v>
@@ -15352,16 +15376,16 @@
     </row>
     <row r="360" spans="1:7">
       <c r="A360" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B360" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="C360" t="s">
-        <v>1418</v>
+        <v>9</v>
       </c>
       <c r="D360" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>1419</v>
@@ -15381,10 +15405,10 @@
         <v>1421</v>
       </c>
       <c r="C361" t="s">
-        <v>9</v>
+        <v>1422</v>
       </c>
       <c r="D361" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>1423</v>
@@ -15393,7 +15417,7 @@
         <v>12</v>
       </c>
       <c r="G361" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362" spans="1:7">
@@ -15407,7 +15431,7 @@
         <v>1426</v>
       </c>
       <c r="D362" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>1427</v>
@@ -15416,7 +15440,7 @@
         <v>12</v>
       </c>
       <c r="G362" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:7">
@@ -15439,7 +15463,7 @@
         <v>12</v>
       </c>
       <c r="G363" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:7">
@@ -15462,7 +15486,7 @@
         <v>12</v>
       </c>
       <c r="G364" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365" spans="1:7">
@@ -15473,10 +15497,10 @@
         <v>1437</v>
       </c>
       <c r="C365" t="s">
+        <v>9</v>
+      </c>
+      <c r="D365" t="s">
         <v>1438</v>
-      </c>
-      <c r="D365" t="s">
-        <v>1430</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>1439</v>
@@ -15485,7 +15509,7 @@
         <v>12</v>
       </c>
       <c r="G365" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366" spans="1:7">
@@ -15499,7 +15523,7 @@
         <v>1442</v>
       </c>
       <c r="D366" t="s">
-        <v>1430</v>
+        <v>1438</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>1443</v>
@@ -15522,30 +15546,30 @@
         <v>1446</v>
       </c>
       <c r="D367" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E367" s="1" t="s">
         <v>1447</v>
       </c>
-      <c r="E367" s="1" t="s">
-        <v>1448</v>
-      </c>
       <c r="F367" t="s">
         <v>12</v>
       </c>
       <c r="G367" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:7">
       <c r="A368" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B368" t="s">
         <v>1449</v>
       </c>
-      <c r="B368" t="s">
+      <c r="C368" t="s">
         <v>1450</v>
       </c>
-      <c r="C368" t="s">
-        <v>9</v>
-      </c>
       <c r="D368" t="s">
-        <v>1447</v>
+        <v>1438</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>1451</v>
@@ -15554,7 +15578,7 @@
         <v>12</v>
       </c>
       <c r="G368" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369" spans="1:7">
@@ -15568,30 +15592,30 @@
         <v>1454</v>
       </c>
       <c r="D369" t="s">
-        <v>1447</v>
+        <v>1455</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="F369" t="s">
         <v>12</v>
       </c>
       <c r="G369" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B370" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C370" t="s">
         <v>9</v>
       </c>
       <c r="D370" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>1459</v>
@@ -15600,7 +15624,7 @@
         <v>12</v>
       </c>
       <c r="G370" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371" spans="1:7">
@@ -15611,10 +15635,10 @@
         <v>1461</v>
       </c>
       <c r="C371" t="s">
-        <v>9</v>
+        <v>1462</v>
       </c>
       <c r="D371" t="s">
-        <v>1462</v>
+        <v>1455</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>1463</v>
@@ -15623,7 +15647,7 @@
         <v>12</v>
       </c>
       <c r="G371" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -15634,10 +15658,10 @@
         <v>1465</v>
       </c>
       <c r="C372" t="s">
+        <v>9</v>
+      </c>
+      <c r="D372" t="s">
         <v>1466</v>
-      </c>
-      <c r="D372" t="s">
-        <v>1462</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>1467</v>
@@ -15669,7 +15693,7 @@
         <v>12</v>
       </c>
       <c r="G373" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374" spans="1:7">
@@ -15683,33 +15707,33 @@
         <v>1474</v>
       </c>
       <c r="D374" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E374" s="1" t="s">
         <v>1475</v>
       </c>
-      <c r="E374" s="1" t="s">
-        <v>1476</v>
-      </c>
       <c r="F374" t="s">
         <v>12</v>
       </c>
       <c r="G374" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375" spans="1:7">
       <c r="A375" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B375" t="s">
         <v>1477</v>
       </c>
-      <c r="B375" t="s">
+      <c r="C375" t="s">
+        <v>9</v>
+      </c>
+      <c r="D375" t="s">
         <v>1478</v>
       </c>
-      <c r="C375" t="s">
+      <c r="E375" s="1" t="s">
         <v>1479</v>
-      </c>
-      <c r="D375" t="s">
-        <v>1475</v>
-      </c>
-      <c r="E375" s="1" t="s">
-        <v>1480</v>
       </c>
       <c r="F375" t="s">
         <v>12</v>
@@ -15720,19 +15744,19 @@
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B376" t="s">
         <v>1481</v>
       </c>
-      <c r="B376" t="s">
+      <c r="C376" t="s">
         <v>1482</v>
       </c>
-      <c r="C376" t="s">
-        <v>9</v>
-      </c>
       <c r="D376" t="s">
-        <v>1475</v>
+        <v>1483</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="F376" t="s">
         <v>12</v>
@@ -15743,39 +15767,39 @@
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B377" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C377" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="D377" t="s">
-        <v>1475</v>
+        <v>1483</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="F377" t="s">
         <v>12</v>
       </c>
       <c r="G377" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378" spans="1:7">
       <c r="A378" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B378" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="C378" t="s">
         <v>9</v>
       </c>
       <c r="D378" t="s">
-        <v>1490</v>
+        <v>1483</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>1491</v>
@@ -15795,10 +15819,10 @@
         <v>1493</v>
       </c>
       <c r="C379" t="s">
-        <v>9</v>
+        <v>1494</v>
       </c>
       <c r="D379" t="s">
-        <v>1494</v>
+        <v>1483</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>1495</v>
@@ -15807,7 +15831,7 @@
         <v>12</v>
       </c>
       <c r="G379" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -15818,10 +15842,10 @@
         <v>1497</v>
       </c>
       <c r="C380" t="s">
+        <v>9</v>
+      </c>
+      <c r="D380" t="s">
         <v>1498</v>
-      </c>
-      <c r="D380" t="s">
-        <v>1494</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>1499</v>
@@ -15841,10 +15865,10 @@
         <v>1501</v>
       </c>
       <c r="C381" t="s">
+        <v>9</v>
+      </c>
+      <c r="D381" t="s">
         <v>1502</v>
-      </c>
-      <c r="D381" t="s">
-        <v>1494</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>1503</v>
@@ -15867,30 +15891,30 @@
         <v>1506</v>
       </c>
       <c r="D382" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E382" s="1" t="s">
         <v>1507</v>
       </c>
-      <c r="E382" s="1" t="s">
-        <v>1508</v>
-      </c>
       <c r="F382" t="s">
         <v>12</v>
       </c>
       <c r="G382" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383" spans="1:7">
       <c r="A383" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B383" t="s">
         <v>1509</v>
       </c>
-      <c r="B383" t="s">
+      <c r="C383" t="s">
         <v>1510</v>
       </c>
-      <c r="C383" t="s">
-        <v>9</v>
-      </c>
       <c r="D383" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>1511</v>
@@ -15910,33 +15934,33 @@
         <v>1513</v>
       </c>
       <c r="C384" t="s">
-        <v>9</v>
+        <v>1514</v>
       </c>
       <c r="D384" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="F384" t="s">
         <v>12</v>
       </c>
       <c r="G384" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B385" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C385" t="s">
-        <v>1518</v>
+        <v>9</v>
       </c>
       <c r="D385" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>1519</v>
@@ -15945,7 +15969,7 @@
         <v>12</v>
       </c>
       <c r="G385" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386" spans="1:7">
@@ -15956,10 +15980,10 @@
         <v>1521</v>
       </c>
       <c r="C386" t="s">
+        <v>9</v>
+      </c>
+      <c r="D386" t="s">
         <v>1522</v>
-      </c>
-      <c r="D386" t="s">
-        <v>1514</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>1523</v>
@@ -15982,7 +16006,7 @@
         <v>1526</v>
       </c>
       <c r="D387" t="s">
-        <v>1514</v>
+        <v>1522</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>1527</v>
@@ -15991,7 +16015,7 @@
         <v>12</v>
       </c>
       <c r="G387" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -16002,10 +16026,10 @@
         <v>1529</v>
       </c>
       <c r="C388" t="s">
-        <v>9</v>
+        <v>1530</v>
       </c>
       <c r="D388" t="s">
-        <v>1530</v>
+        <v>1522</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>1531</v>
@@ -16025,10 +16049,10 @@
         <v>1533</v>
       </c>
       <c r="C389" t="s">
-        <v>9</v>
+        <v>1534</v>
       </c>
       <c r="D389" t="s">
-        <v>1534</v>
+        <v>1522</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>1535</v>
@@ -16060,7 +16084,7 @@
         <v>12</v>
       </c>
       <c r="G390" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391" spans="1:7">
@@ -16071,10 +16095,10 @@
         <v>1541</v>
       </c>
       <c r="C391" t="s">
+        <v>9</v>
+      </c>
+      <c r="D391" t="s">
         <v>1542</v>
-      </c>
-      <c r="D391" t="s">
-        <v>1538</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>1543</v>
@@ -16083,7 +16107,7 @@
         <v>12</v>
       </c>
       <c r="G391" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392" spans="1:7">
@@ -16094,10 +16118,10 @@
         <v>1545</v>
       </c>
       <c r="C392" t="s">
+        <v>9</v>
+      </c>
+      <c r="D392" t="s">
         <v>1546</v>
-      </c>
-      <c r="D392" t="s">
-        <v>1538</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>1547</v>
@@ -16106,7 +16130,7 @@
         <v>12</v>
       </c>
       <c r="G392" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393" spans="1:7">
@@ -16117,10 +16141,10 @@
         <v>1549</v>
       </c>
       <c r="C393" t="s">
-        <v>9</v>
+        <v>1550</v>
       </c>
       <c r="D393" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>1551</v>
@@ -16129,7 +16153,7 @@
         <v>12</v>
       </c>
       <c r="G393" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -16140,10 +16164,10 @@
         <v>1553</v>
       </c>
       <c r="C394" t="s">
-        <v>9</v>
+        <v>1554</v>
       </c>
       <c r="D394" t="s">
-        <v>1554</v>
+        <v>1546</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>1555</v>
@@ -16152,7 +16176,7 @@
         <v>12</v>
       </c>
       <c r="G394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395" spans="1:7">
@@ -16163,10 +16187,10 @@
         <v>1557</v>
       </c>
       <c r="C395" t="s">
+        <v>9</v>
+      </c>
+      <c r="D395" t="s">
         <v>1558</v>
-      </c>
-      <c r="D395" t="s">
-        <v>1554</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>1559</v>
@@ -16175,7 +16199,7 @@
         <v>12</v>
       </c>
       <c r="G395" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396" spans="1:7">
@@ -16232,10 +16256,10 @@
         <v>1569</v>
       </c>
       <c r="C398" t="s">
+        <v>9</v>
+      </c>
+      <c r="D398" t="s">
         <v>1570</v>
-      </c>
-      <c r="D398" t="s">
-        <v>1562</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>1571</v>
@@ -16244,7 +16268,7 @@
         <v>12</v>
       </c>
       <c r="G398" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399" spans="1:7">
@@ -16255,10 +16279,10 @@
         <v>1573</v>
       </c>
       <c r="C399" t="s">
-        <v>9</v>
+        <v>1574</v>
       </c>
       <c r="D399" t="s">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>1575</v>
@@ -16267,7 +16291,7 @@
         <v>12</v>
       </c>
       <c r="G399" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400" spans="1:7">
@@ -16278,10 +16302,10 @@
         <v>1577</v>
       </c>
       <c r="C400" t="s">
-        <v>9</v>
+        <v>1578</v>
       </c>
       <c r="D400" t="s">
-        <v>1578</v>
+        <v>1570</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>1579</v>
@@ -16301,10 +16325,10 @@
         <v>1581</v>
       </c>
       <c r="C401" t="s">
+        <v>9</v>
+      </c>
+      <c r="D401" t="s">
         <v>1582</v>
-      </c>
-      <c r="D401" t="s">
-        <v>1578</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>1583</v>
@@ -16313,7 +16337,7 @@
         <v>12</v>
       </c>
       <c r="G401" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402" spans="1:7">
@@ -16382,7 +16406,7 @@
         <v>12</v>
       </c>
       <c r="G404" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405" spans="1:7">
@@ -16416,16 +16440,16 @@
         <v>1601</v>
       </c>
       <c r="C406" t="s">
+        <v>9</v>
+      </c>
+      <c r="D406" t="s">
         <v>1602</v>
-      </c>
-      <c r="D406" t="s">
-        <v>1594</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>1603</v>
       </c>
       <c r="F406" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G406" t="b">
         <v>0</v>
@@ -16442,7 +16466,7 @@
         <v>1606</v>
       </c>
       <c r="D407" t="s">
-        <v>1594</v>
+        <v>1602</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>1607</v>
@@ -16465,13 +16489,13 @@
         <v>1610</v>
       </c>
       <c r="D408" t="s">
-        <v>1594</v>
+        <v>1602</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>1611</v>
       </c>
       <c r="F408" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G408" t="b">
         <v>0</v>
@@ -16488,7 +16512,7 @@
         <v>1614</v>
       </c>
       <c r="D409" t="s">
-        <v>1594</v>
+        <v>1602</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>1615</v>
@@ -16497,7 +16521,7 @@
         <v>12</v>
       </c>
       <c r="G409" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410" spans="1:7">
@@ -16508,10 +16532,10 @@
         <v>1617</v>
       </c>
       <c r="C410" t="s">
-        <v>9</v>
+        <v>1618</v>
       </c>
       <c r="D410" t="s">
-        <v>1618</v>
+        <v>1602</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>1619</v>
@@ -16534,7 +16558,7 @@
         <v>1622</v>
       </c>
       <c r="D411" t="s">
-        <v>1618</v>
+        <v>1602</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>1623</v>
@@ -16543,7 +16567,7 @@
         <v>12</v>
       </c>
       <c r="G411" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412" spans="1:7">
@@ -16554,10 +16578,10 @@
         <v>1625</v>
       </c>
       <c r="C412" t="s">
+        <v>9</v>
+      </c>
+      <c r="D412" t="s">
         <v>1626</v>
-      </c>
-      <c r="D412" t="s">
-        <v>1618</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>1627</v>
@@ -16566,7 +16590,7 @@
         <v>12</v>
       </c>
       <c r="G412" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413" spans="1:7">
@@ -16580,7 +16604,7 @@
         <v>1630</v>
       </c>
       <c r="D413" t="s">
-        <v>1618</v>
+        <v>1626</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>1631</v>
@@ -16600,10 +16624,10 @@
         <v>1633</v>
       </c>
       <c r="C414" t="s">
-        <v>9</v>
+        <v>1634</v>
       </c>
       <c r="D414" t="s">
-        <v>1634</v>
+        <v>1626</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>1635</v>
@@ -16612,7 +16636,7 @@
         <v>12</v>
       </c>
       <c r="G414" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415" spans="1:7">
@@ -16623,10 +16647,10 @@
         <v>1637</v>
       </c>
       <c r="C415" t="s">
-        <v>9</v>
+        <v>1638</v>
       </c>
       <c r="D415" t="s">
-        <v>1638</v>
+        <v>1626</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>1639</v>
@@ -16635,7 +16659,7 @@
         <v>12</v>
       </c>
       <c r="G415" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416" spans="1:7">
@@ -16692,10 +16716,10 @@
         <v>1649</v>
       </c>
       <c r="C418" t="s">
+        <v>9</v>
+      </c>
+      <c r="D418" t="s">
         <v>1650</v>
-      </c>
-      <c r="D418" t="s">
-        <v>1646</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>1651</v>
@@ -16715,10 +16739,10 @@
         <v>1653</v>
       </c>
       <c r="C419" t="s">
+        <v>9</v>
+      </c>
+      <c r="D419" t="s">
         <v>1654</v>
-      </c>
-      <c r="D419" t="s">
-        <v>1646</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>1655</v>
@@ -16738,10 +16762,10 @@
         <v>1657</v>
       </c>
       <c r="C420" t="s">
-        <v>9</v>
+        <v>1658</v>
       </c>
       <c r="D420" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>1659</v>
@@ -16764,7 +16788,7 @@
         <v>1662</v>
       </c>
       <c r="D421" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>1663</v>
@@ -16796,7 +16820,7 @@
         <v>12</v>
       </c>
       <c r="G422" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423" spans="1:7">
@@ -16807,10 +16831,10 @@
         <v>1669</v>
       </c>
       <c r="C423" t="s">
-        <v>9</v>
+        <v>1670</v>
       </c>
       <c r="D423" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>1671</v>
@@ -16830,10 +16854,10 @@
         <v>1673</v>
       </c>
       <c r="C424" t="s">
+        <v>9</v>
+      </c>
+      <c r="D424" t="s">
         <v>1674</v>
-      </c>
-      <c r="D424" t="s">
-        <v>1670</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>1675</v>
@@ -16853,10 +16877,10 @@
         <v>1677</v>
       </c>
       <c r="C425" t="s">
+        <v>9</v>
+      </c>
+      <c r="D425" t="s">
         <v>1678</v>
-      </c>
-      <c r="D425" t="s">
-        <v>1670</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>1679</v>
@@ -16865,7 +16889,7 @@
         <v>12</v>
       </c>
       <c r="G425" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426" spans="1:7">
@@ -16876,10 +16900,10 @@
         <v>1681</v>
       </c>
       <c r="C426" t="s">
-        <v>9</v>
+        <v>1682</v>
       </c>
       <c r="D426" t="s">
-        <v>1682</v>
+        <v>1678</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>1683</v>
@@ -16888,7 +16912,7 @@
         <v>12</v>
       </c>
       <c r="G426" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427" spans="1:7">
@@ -16902,7 +16926,7 @@
         <v>1686</v>
       </c>
       <c r="D427" t="s">
-        <v>1682</v>
+        <v>1678</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>1687</v>
@@ -16911,7 +16935,7 @@
         <v>12</v>
       </c>
       <c r="G427" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428" spans="1:7">
@@ -16945,10 +16969,10 @@
         <v>1693</v>
       </c>
       <c r="C429" t="s">
-        <v>9</v>
+        <v>1694</v>
       </c>
       <c r="D429" t="s">
-        <v>1694</v>
+        <v>1690</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>1695</v>
@@ -16968,10 +16992,10 @@
         <v>1697</v>
       </c>
       <c r="C430" t="s">
+        <v>9</v>
+      </c>
+      <c r="D430" t="s">
         <v>1698</v>
-      </c>
-      <c r="D430" t="s">
-        <v>1694</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>1699</v>
@@ -16980,7 +17004,7 @@
         <v>12</v>
       </c>
       <c r="G430" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431" spans="1:7">
@@ -16991,13 +17015,13 @@
         <v>1701</v>
       </c>
       <c r="C431" t="s">
+        <v>9</v>
+      </c>
+      <c r="D431" t="s">
         <v>1702</v>
       </c>
-      <c r="D431" t="s">
+      <c r="E431" s="1" t="s">
         <v>1703</v>
-      </c>
-      <c r="E431" s="1" t="s">
-        <v>1704</v>
       </c>
       <c r="F431" t="s">
         <v>12</v>
@@ -17008,16 +17032,16 @@
     </row>
     <row r="432" spans="1:7">
       <c r="A432" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B432" t="s">
         <v>1705</v>
       </c>
-      <c r="B432" t="s">
+      <c r="C432" t="s">
         <v>1706</v>
       </c>
-      <c r="C432" t="s">
-        <v>9</v>
-      </c>
       <c r="D432" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>1707</v>
@@ -17026,7 +17050,7 @@
         <v>12</v>
       </c>
       <c r="G432" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433" spans="1:7">
@@ -17040,30 +17064,30 @@
         <v>1710</v>
       </c>
       <c r="D433" t="s">
-        <v>1703</v>
+        <v>1711</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="F433" t="s">
         <v>12</v>
       </c>
       <c r="G433" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434" spans="1:7">
       <c r="A434" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B434" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="C434" t="s">
         <v>9</v>
       </c>
       <c r="D434" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>1715</v>
@@ -17086,7 +17110,7 @@
         <v>1718</v>
       </c>
       <c r="D435" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>1719</v>
@@ -17106,10 +17130,10 @@
         <v>1721</v>
       </c>
       <c r="C436" t="s">
+        <v>9</v>
+      </c>
+      <c r="D436" t="s">
         <v>1722</v>
-      </c>
-      <c r="D436" t="s">
-        <v>1714</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>1723</v>
@@ -17118,7 +17142,7 @@
         <v>12</v>
       </c>
       <c r="G436" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437" spans="1:7">
@@ -17129,10 +17153,10 @@
         <v>1725</v>
       </c>
       <c r="C437" t="s">
-        <v>9</v>
+        <v>1726</v>
       </c>
       <c r="D437" t="s">
-        <v>1726</v>
+        <v>1722</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>1727</v>
@@ -17155,7 +17179,7 @@
         <v>1730</v>
       </c>
       <c r="D438" t="s">
-        <v>1726</v>
+        <v>1722</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>1731</v>
@@ -17164,7 +17188,7 @@
         <v>12</v>
       </c>
       <c r="G438" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439" spans="1:7">
@@ -17175,10 +17199,10 @@
         <v>1733</v>
       </c>
       <c r="C439" t="s">
+        <v>9</v>
+      </c>
+      <c r="D439" t="s">
         <v>1734</v>
-      </c>
-      <c r="D439" t="s">
-        <v>1726</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>1735</v>
@@ -17187,7 +17211,7 @@
         <v>12</v>
       </c>
       <c r="G439" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440" spans="1:7">
@@ -17198,10 +17222,10 @@
         <v>1737</v>
       </c>
       <c r="C440" t="s">
-        <v>9</v>
+        <v>1738</v>
       </c>
       <c r="D440" t="s">
-        <v>1738</v>
+        <v>1734</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>1739</v>
@@ -17224,30 +17248,30 @@
         <v>1742</v>
       </c>
       <c r="D441" t="s">
+        <v>1734</v>
+      </c>
+      <c r="E441" s="1" t="s">
         <v>1743</v>
       </c>
-      <c r="E441" s="1" t="s">
-        <v>1744</v>
-      </c>
       <c r="F441" t="s">
         <v>12</v>
       </c>
       <c r="G441" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="442" spans="1:7">
       <c r="A442" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B442" t="s">
         <v>1745</v>
       </c>
-      <c r="B442" t="s">
+      <c r="C442" t="s">
+        <v>9</v>
+      </c>
+      <c r="D442" t="s">
         <v>1746</v>
-      </c>
-      <c r="C442" t="s">
-        <v>9</v>
-      </c>
-      <c r="D442" t="s">
-        <v>1743</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>1747</v>
@@ -17256,7 +17280,7 @@
         <v>12</v>
       </c>
       <c r="G442" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443" spans="1:7">
@@ -17267,33 +17291,33 @@
         <v>1749</v>
       </c>
       <c r="C443" t="s">
-        <v>9</v>
+        <v>1750</v>
       </c>
       <c r="D443" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="F443" t="s">
         <v>12</v>
       </c>
       <c r="G443" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444" spans="1:7">
       <c r="A444" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B444" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="C444" t="s">
         <v>9</v>
       </c>
       <c r="D444" t="s">
-        <v>1754</v>
+        <v>1751</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>1755</v>
@@ -17302,7 +17326,7 @@
         <v>12</v>
       </c>
       <c r="G444" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445" spans="1:7">
@@ -17313,16 +17337,16 @@
         <v>1757</v>
       </c>
       <c r="C445" t="s">
+        <v>9</v>
+      </c>
+      <c r="D445" t="s">
         <v>1758</v>
       </c>
-      <c r="D445" t="s">
+      <c r="E445" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="E445" s="1" t="s">
-        <v>1760</v>
-      </c>
       <c r="F445" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G445" t="b">
         <v>0</v>
@@ -17330,16 +17354,16 @@
     </row>
     <row r="446" spans="1:7">
       <c r="A446" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B446" t="s">
         <v>1761</v>
       </c>
-      <c r="B446" t="s">
+      <c r="C446" t="s">
+        <v>9</v>
+      </c>
+      <c r="D446" t="s">
         <v>1762</v>
-      </c>
-      <c r="C446" t="s">
-        <v>9</v>
-      </c>
-      <c r="D446" t="s">
-        <v>1759</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>1763</v>
@@ -17362,10 +17386,10 @@
         <v>1766</v>
       </c>
       <c r="D447" t="s">
-        <v>1759</v>
+        <v>1767</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="F447" t="s">
         <v>165</v>
@@ -17376,16 +17400,16 @@
     </row>
     <row r="448" spans="1:7">
       <c r="A448" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B448" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="C448" t="s">
-        <v>1770</v>
+        <v>9</v>
       </c>
       <c r="D448" t="s">
-        <v>1759</v>
+        <v>1767</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>1771</v>
@@ -17394,7 +17418,7 @@
         <v>12</v>
       </c>
       <c r="G448" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="449" spans="1:7">
@@ -17408,13 +17432,13 @@
         <v>1774</v>
       </c>
       <c r="D449" t="s">
+        <v>1767</v>
+      </c>
+      <c r="E449" s="1" t="s">
         <v>1775</v>
       </c>
-      <c r="E449" s="1" t="s">
-        <v>1776</v>
-      </c>
       <c r="F449" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G449" t="b">
         <v>0</v>
@@ -17422,16 +17446,16 @@
     </row>
     <row r="450" spans="1:7">
       <c r="A450" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B450" t="s">
         <v>1777</v>
       </c>
-      <c r="B450" t="s">
+      <c r="C450" t="s">
         <v>1778</v>
       </c>
-      <c r="C450" t="s">
-        <v>9</v>
-      </c>
       <c r="D450" t="s">
-        <v>1775</v>
+        <v>1767</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>1779</v>
@@ -17440,7 +17464,7 @@
         <v>12</v>
       </c>
       <c r="G450" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451" spans="1:7">
@@ -17454,30 +17478,30 @@
         <v>1782</v>
       </c>
       <c r="D451" t="s">
-        <v>1775</v>
+        <v>1783</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="F451" t="s">
         <v>12</v>
       </c>
       <c r="G451" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452" spans="1:7">
       <c r="A452" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B452" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="C452" t="s">
         <v>9</v>
       </c>
       <c r="D452" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>1787</v>
@@ -17497,10 +17521,10 @@
         <v>1789</v>
       </c>
       <c r="C453" t="s">
-        <v>9</v>
+        <v>1790</v>
       </c>
       <c r="D453" t="s">
-        <v>1790</v>
+        <v>1783</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>1791</v>
@@ -17509,7 +17533,7 @@
         <v>12</v>
       </c>
       <c r="G453" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454" spans="1:7">
@@ -17520,10 +17544,10 @@
         <v>1793</v>
       </c>
       <c r="C454" t="s">
+        <v>9</v>
+      </c>
+      <c r="D454" t="s">
         <v>1794</v>
-      </c>
-      <c r="D454" t="s">
-        <v>1790</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>1795</v>
@@ -17532,7 +17556,7 @@
         <v>12</v>
       </c>
       <c r="G454" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455" spans="1:7">
@@ -17543,10 +17567,10 @@
         <v>1797</v>
       </c>
       <c r="C455" t="s">
+        <v>9</v>
+      </c>
+      <c r="D455" t="s">
         <v>1798</v>
-      </c>
-      <c r="D455" t="s">
-        <v>1790</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>1799</v>
@@ -17555,7 +17579,7 @@
         <v>12</v>
       </c>
       <c r="G455" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456" spans="1:7">
@@ -17566,10 +17590,10 @@
         <v>1801</v>
       </c>
       <c r="C456" t="s">
-        <v>9</v>
+        <v>1802</v>
       </c>
       <c r="D456" t="s">
-        <v>1802</v>
+        <v>1798</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>1803</v>
@@ -17578,7 +17602,7 @@
         <v>12</v>
       </c>
       <c r="G456" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457" spans="1:7">
@@ -17589,10 +17613,10 @@
         <v>1805</v>
       </c>
       <c r="C457" t="s">
-        <v>9</v>
+        <v>1806</v>
       </c>
       <c r="D457" t="s">
-        <v>1806</v>
+        <v>1798</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>1807</v>
@@ -17601,7 +17625,7 @@
         <v>12</v>
       </c>
       <c r="G457" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458" spans="1:7">
@@ -17612,10 +17636,10 @@
         <v>1809</v>
       </c>
       <c r="C458" t="s">
+        <v>9</v>
+      </c>
+      <c r="D458" t="s">
         <v>1810</v>
-      </c>
-      <c r="D458" t="s">
-        <v>1806</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>1811</v>
@@ -17624,7 +17648,7 @@
         <v>12</v>
       </c>
       <c r="G458" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="459" spans="1:7">
@@ -17635,10 +17659,10 @@
         <v>1813</v>
       </c>
       <c r="C459" t="s">
+        <v>9</v>
+      </c>
+      <c r="D459" t="s">
         <v>1814</v>
-      </c>
-      <c r="D459" t="s">
-        <v>1806</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>1815</v>
@@ -17661,59 +17685,59 @@
         <v>1818</v>
       </c>
       <c r="D460" t="s">
-        <v>1806</v>
+        <v>1814</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>1815</v>
+        <v>1819</v>
       </c>
       <c r="F460" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G460" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461" spans="1:7">
       <c r="A461" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B461" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="C461" t="s">
-        <v>9</v>
+        <v>1822</v>
       </c>
       <c r="D461" t="s">
-        <v>1821</v>
+        <v>1814</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="F461" t="s">
         <v>12</v>
       </c>
       <c r="G461" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="462" spans="1:7">
       <c r="A462" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C462" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D462" t="s">
+        <v>1814</v>
+      </c>
+      <c r="E462" s="1" t="s">
         <v>1823</v>
       </c>
-      <c r="B462" t="s">
-        <v>1824</v>
-      </c>
-      <c r="C462" t="s">
-        <v>1825</v>
-      </c>
-      <c r="D462" t="s">
-        <v>1821</v>
-      </c>
-      <c r="E462" s="1" t="s">
-        <v>1826</v>
-      </c>
       <c r="F462" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G462" t="b">
         <v>0</v>
@@ -17727,10 +17751,10 @@
         <v>1828</v>
       </c>
       <c r="C463" t="s">
+        <v>9</v>
+      </c>
+      <c r="D463" t="s">
         <v>1829</v>
-      </c>
-      <c r="D463" t="s">
-        <v>1821</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>1830</v>
@@ -17739,7 +17763,7 @@
         <v>12</v>
       </c>
       <c r="G463" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -17750,10 +17774,10 @@
         <v>1832</v>
       </c>
       <c r="C464" t="s">
-        <v>9</v>
+        <v>1833</v>
       </c>
       <c r="D464" t="s">
-        <v>1833</v>
+        <v>1829</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>1834</v>
@@ -17773,10 +17797,10 @@
         <v>1836</v>
       </c>
       <c r="C465" t="s">
-        <v>9</v>
+        <v>1837</v>
       </c>
       <c r="D465" t="s">
-        <v>1837</v>
+        <v>1829</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>1838</v>
@@ -17785,7 +17809,7 @@
         <v>12</v>
       </c>
       <c r="G465" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="466" spans="1:7">
@@ -17796,10 +17820,10 @@
         <v>1840</v>
       </c>
       <c r="C466" t="s">
+        <v>9</v>
+      </c>
+      <c r="D466" t="s">
         <v>1841</v>
-      </c>
-      <c r="D466" t="s">
-        <v>1837</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>1842</v>
@@ -17808,7 +17832,7 @@
         <v>12</v>
       </c>
       <c r="G466" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467" spans="1:7">
@@ -17854,7 +17878,7 @@
         <v>12</v>
       </c>
       <c r="G468" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469" spans="1:7">
@@ -17877,7 +17901,7 @@
         <v>12</v>
       </c>
       <c r="G469" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="470" spans="1:7">
@@ -17888,10 +17912,10 @@
         <v>1856</v>
       </c>
       <c r="C470" t="s">
-        <v>9</v>
+        <v>1857</v>
       </c>
       <c r="D470" t="s">
-        <v>1857</v>
+        <v>1853</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>1858</v>
@@ -17911,10 +17935,13 @@
         <v>1860</v>
       </c>
       <c r="C471" t="s">
+        <v>9</v>
+      </c>
+      <c r="D471" t="s">
         <v>1861</v>
       </c>
-      <c r="D471" t="s">
-        <v>1857</v>
+      <c r="E471" s="1" t="s">
+        <v>1862</v>
       </c>
       <c r="F471" t="s">
         <v>12</v>
@@ -17925,19 +17952,19 @@
     </row>
     <row r="472" spans="1:7">
       <c r="A472" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B472" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="C472" t="s">
         <v>9</v>
       </c>
       <c r="D472" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="F472" t="s">
         <v>12</v>
@@ -17948,19 +17975,16 @@
     </row>
     <row r="473" spans="1:7">
       <c r="A473" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B473" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="C473" t="s">
-        <v>9</v>
+        <v>1869</v>
       </c>
       <c r="D473" t="s">
-        <v>1868</v>
-      </c>
-      <c r="E473" s="1" t="s">
-        <v>1869</v>
+        <v>1865</v>
       </c>
       <c r="F473" t="s">
         <v>12</v>
@@ -17977,10 +18001,10 @@
         <v>1871</v>
       </c>
       <c r="C474" t="s">
+        <v>9</v>
+      </c>
+      <c r="D474" t="s">
         <v>1872</v>
-      </c>
-      <c r="D474" t="s">
-        <v>1868</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>1873</v>
@@ -18023,10 +18047,10 @@
         <v>1879</v>
       </c>
       <c r="C476" t="s">
-        <v>9</v>
+        <v>1880</v>
       </c>
       <c r="D476" t="s">
-        <v>1880</v>
+        <v>1876</v>
       </c>
       <c r="E476" s="1" t="s">
         <v>1881</v>
@@ -18046,33 +18070,33 @@
         <v>1883</v>
       </c>
       <c r="C477" t="s">
+        <v>9</v>
+      </c>
+      <c r="D477" t="s">
         <v>1884</v>
       </c>
-      <c r="D477" t="s">
+      <c r="E477" s="1" t="s">
         <v>1885</v>
       </c>
-      <c r="E477" s="1" t="s">
-        <v>1886</v>
-      </c>
       <c r="F477" t="s">
         <v>12</v>
       </c>
       <c r="G477" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="478" spans="1:7">
       <c r="A478" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B478" t="s">
         <v>1887</v>
       </c>
-      <c r="B478" t="s">
+      <c r="C478" t="s">
+        <v>9</v>
+      </c>
+      <c r="D478" t="s">
         <v>1888</v>
-      </c>
-      <c r="C478" t="s">
-        <v>9</v>
-      </c>
-      <c r="D478" t="s">
-        <v>1885</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>1889</v>
@@ -18081,7 +18105,7 @@
         <v>12</v>
       </c>
       <c r="G478" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479" spans="1:7">
@@ -18092,33 +18116,33 @@
         <v>1891</v>
       </c>
       <c r="C479" t="s">
-        <v>9</v>
+        <v>1892</v>
       </c>
       <c r="D479" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="F479" t="s">
         <v>12</v>
       </c>
       <c r="G479" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480" spans="1:7">
       <c r="A480" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B480" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="C480" t="s">
         <v>9</v>
       </c>
       <c r="D480" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>1897</v>
@@ -18184,10 +18208,10 @@
         <v>1907</v>
       </c>
       <c r="C483" t="s">
+        <v>9</v>
+      </c>
+      <c r="D483" t="s">
         <v>1908</v>
-      </c>
-      <c r="D483" t="s">
-        <v>1904</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>1909</v>
@@ -18196,7 +18220,7 @@
         <v>12</v>
       </c>
       <c r="G483" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="484" spans="1:7">
@@ -18207,10 +18231,10 @@
         <v>1911</v>
       </c>
       <c r="C484" t="s">
+        <v>9</v>
+      </c>
+      <c r="D484" t="s">
         <v>1912</v>
-      </c>
-      <c r="D484" t="s">
-        <v>1904</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>1913</v>
@@ -18219,7 +18243,7 @@
         <v>12</v>
       </c>
       <c r="G484" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485" spans="1:7">
@@ -18230,10 +18254,10 @@
         <v>1915</v>
       </c>
       <c r="C485" t="s">
-        <v>9</v>
+        <v>1916</v>
       </c>
       <c r="D485" t="s">
-        <v>1916</v>
+        <v>1912</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>1917</v>
@@ -18242,7 +18266,7 @@
         <v>12</v>
       </c>
       <c r="G485" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486" spans="1:7">
@@ -18256,7 +18280,7 @@
         <v>1920</v>
       </c>
       <c r="D486" t="s">
-        <v>1916</v>
+        <v>1912</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>1921</v>
@@ -18276,10 +18300,10 @@
         <v>1923</v>
       </c>
       <c r="C487" t="s">
+        <v>9</v>
+      </c>
+      <c r="D487" t="s">
         <v>1924</v>
-      </c>
-      <c r="D487" t="s">
-        <v>1916</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>1925</v>
@@ -18299,10 +18323,10 @@
         <v>1927</v>
       </c>
       <c r="C488" t="s">
-        <v>9</v>
+        <v>1928</v>
       </c>
       <c r="D488" t="s">
-        <v>1928</v>
+        <v>1924</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>1929</v>
@@ -18325,7 +18349,7 @@
         <v>1932</v>
       </c>
       <c r="D489" t="s">
-        <v>1928</v>
+        <v>1924</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>1933</v>
@@ -18368,10 +18392,10 @@
         <v>1939</v>
       </c>
       <c r="C491" t="s">
-        <v>9</v>
+        <v>1940</v>
       </c>
       <c r="D491" t="s">
-        <v>1940</v>
+        <v>1936</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>1941</v>
@@ -18380,7 +18404,7 @@
         <v>12</v>
       </c>
       <c r="G491" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="492" spans="1:7">
@@ -18426,7 +18450,7 @@
         <v>12</v>
       </c>
       <c r="G493" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494" spans="1:7">
@@ -18437,10 +18461,10 @@
         <v>1951</v>
       </c>
       <c r="C494" t="s">
+        <v>9</v>
+      </c>
+      <c r="D494" t="s">
         <v>1952</v>
-      </c>
-      <c r="D494" t="s">
-        <v>1948</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>1953</v>
@@ -18483,10 +18507,10 @@
         <v>1959</v>
       </c>
       <c r="C496" t="s">
-        <v>9</v>
+        <v>1960</v>
       </c>
       <c r="D496" t="s">
-        <v>1960</v>
+        <v>1956</v>
       </c>
       <c r="E496" s="1" t="s">
         <v>1961</v>
@@ -18506,10 +18530,10 @@
         <v>1963</v>
       </c>
       <c r="C497" t="s">
+        <v>9</v>
+      </c>
+      <c r="D497" t="s">
         <v>1964</v>
-      </c>
-      <c r="D497" t="s">
-        <v>1960</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>1965</v>
@@ -18518,7 +18542,7 @@
         <v>12</v>
       </c>
       <c r="G497" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498" spans="1:7">
@@ -18529,10 +18553,10 @@
         <v>1967</v>
       </c>
       <c r="C498" t="s">
+        <v>9</v>
+      </c>
+      <c r="D498" t="s">
         <v>1968</v>
-      </c>
-      <c r="D498" t="s">
-        <v>1960</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>1969</v>
@@ -18555,7 +18579,7 @@
         <v>1972</v>
       </c>
       <c r="D499" t="s">
-        <v>1960</v>
+        <v>1968</v>
       </c>
       <c r="E499" s="1" t="s">
         <v>1973</v>
@@ -18564,7 +18588,7 @@
         <v>12</v>
       </c>
       <c r="G499" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500" spans="1:7">
@@ -18575,10 +18599,10 @@
         <v>1975</v>
       </c>
       <c r="C500" t="s">
-        <v>9</v>
+        <v>1976</v>
       </c>
       <c r="D500" t="s">
-        <v>1976</v>
+        <v>1968</v>
       </c>
       <c r="E500" s="1" t="s">
         <v>1977</v>
@@ -18598,10 +18622,10 @@
         <v>1979</v>
       </c>
       <c r="C501" t="s">
-        <v>9</v>
+        <v>1980</v>
       </c>
       <c r="D501" t="s">
-        <v>1980</v>
+        <v>1968</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>1981</v>
@@ -18644,13 +18668,13 @@
         <v>1987</v>
       </c>
       <c r="C503" t="s">
+        <v>9</v>
+      </c>
+      <c r="D503" t="s">
         <v>1988</v>
       </c>
-      <c r="D503" t="s">
+      <c r="E503" s="1" t="s">
         <v>1989</v>
-      </c>
-      <c r="E503" s="1" t="s">
-        <v>1990</v>
       </c>
       <c r="F503" t="s">
         <v>12</v>
@@ -18661,16 +18685,16 @@
     </row>
     <row r="504" spans="1:7">
       <c r="A504" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B504" t="s">
         <v>1991</v>
       </c>
-      <c r="B504" t="s">
+      <c r="C504" t="s">
+        <v>9</v>
+      </c>
+      <c r="D504" t="s">
         <v>1992</v>
-      </c>
-      <c r="C504" t="s">
-        <v>9</v>
-      </c>
-      <c r="D504" t="s">
-        <v>1989</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>1993</v>
@@ -18679,7 +18703,7 @@
         <v>12</v>
       </c>
       <c r="G504" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="505" spans="1:7">
@@ -18693,30 +18717,30 @@
         <v>1996</v>
       </c>
       <c r="D505" t="s">
-        <v>1989</v>
+        <v>1997</v>
       </c>
       <c r="E505" s="1" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="F505" t="s">
         <v>12</v>
       </c>
       <c r="G505" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="506" spans="1:7">
       <c r="A506" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="B506" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C506" t="s">
-        <v>2000</v>
+        <v>9</v>
       </c>
       <c r="D506" t="s">
-        <v>1989</v>
+        <v>1997</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>2001</v>
@@ -18725,7 +18749,7 @@
         <v>12</v>
       </c>
       <c r="G506" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507" spans="1:7">
@@ -18736,10 +18760,10 @@
         <v>2003</v>
       </c>
       <c r="C507" t="s">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="D507" t="s">
-        <v>2004</v>
+        <v>1997</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>2005</v>
@@ -18748,7 +18772,7 @@
         <v>12</v>
       </c>
       <c r="G507" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508" spans="1:7">
@@ -18762,7 +18786,7 @@
         <v>2008</v>
       </c>
       <c r="D508" t="s">
-        <v>2004</v>
+        <v>1997</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>2009</v>
@@ -18782,13 +18806,13 @@
         <v>2011</v>
       </c>
       <c r="C509" t="s">
+        <v>9</v>
+      </c>
+      <c r="D509" t="s">
         <v>2012</v>
       </c>
-      <c r="D509" t="s">
+      <c r="E509" s="1" t="s">
         <v>2013</v>
-      </c>
-      <c r="E509" s="1" t="s">
-        <v>2014</v>
       </c>
       <c r="F509" t="s">
         <v>12</v>
@@ -18799,16 +18823,16 @@
     </row>
     <row r="510" spans="1:7">
       <c r="A510" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B510" t="s">
         <v>2015</v>
       </c>
-      <c r="B510" t="s">
+      <c r="C510" t="s">
         <v>2016</v>
       </c>
-      <c r="C510" t="s">
-        <v>9</v>
-      </c>
       <c r="D510" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>2017</v>
@@ -18817,7 +18841,7 @@
         <v>12</v>
       </c>
       <c r="G510" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -18831,13 +18855,13 @@
         <v>2020</v>
       </c>
       <c r="D511" t="s">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F511" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G511" t="b">
         <v>0</v>
@@ -18845,16 +18869,16 @@
     </row>
     <row r="512" spans="1:7">
       <c r="A512" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B512" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C512" t="s">
-        <v>2024</v>
+        <v>9</v>
       </c>
       <c r="D512" t="s">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>2025</v>
@@ -18877,16 +18901,16 @@
         <v>2028</v>
       </c>
       <c r="D513" t="s">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>2029</v>
       </c>
       <c r="F513" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G513" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -18897,10 +18921,10 @@
         <v>2031</v>
       </c>
       <c r="C514" t="s">
-        <v>9</v>
+        <v>2032</v>
       </c>
       <c r="D514" t="s">
-        <v>2032</v>
+        <v>2021</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>2033</v>
@@ -18909,7 +18933,7 @@
         <v>12</v>
       </c>
       <c r="G514" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515" spans="1:7">
@@ -18920,10 +18944,10 @@
         <v>2035</v>
       </c>
       <c r="C515" t="s">
-        <v>9</v>
+        <v>2036</v>
       </c>
       <c r="D515" t="s">
-        <v>2036</v>
+        <v>2021</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>2037</v>
@@ -18932,7 +18956,7 @@
         <v>12</v>
       </c>
       <c r="G515" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="516" spans="1:7">
@@ -18943,16 +18967,16 @@
         <v>2039</v>
       </c>
       <c r="C516" t="s">
+        <v>9</v>
+      </c>
+      <c r="D516" t="s">
         <v>2040</v>
-      </c>
-      <c r="D516" t="s">
-        <v>2036</v>
       </c>
       <c r="E516" s="1" t="s">
         <v>2041</v>
       </c>
       <c r="F516" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G516" t="b">
         <v>0</v>
@@ -18966,10 +18990,10 @@
         <v>2043</v>
       </c>
       <c r="C517" t="s">
+        <v>9</v>
+      </c>
+      <c r="D517" t="s">
         <v>2044</v>
-      </c>
-      <c r="D517" t="s">
-        <v>2036</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>2045</v>
@@ -18992,16 +19016,16 @@
         <v>2048</v>
       </c>
       <c r="D518" t="s">
-        <v>2036</v>
+        <v>2044</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>2049</v>
       </c>
       <c r="F518" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G518" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="519" spans="1:7">
@@ -19015,7 +19039,7 @@
         <v>2052</v>
       </c>
       <c r="D519" t="s">
-        <v>2036</v>
+        <v>2044</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>2053</v>
@@ -19035,10 +19059,10 @@
         <v>2055</v>
       </c>
       <c r="C520" t="s">
-        <v>9</v>
+        <v>2056</v>
       </c>
       <c r="D520" t="s">
-        <v>2056</v>
+        <v>2044</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>2057</v>
@@ -19047,7 +19071,7 @@
         <v>12</v>
       </c>
       <c r="G520" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521" spans="1:7">
@@ -19058,10 +19082,10 @@
         <v>2059</v>
       </c>
       <c r="C521" t="s">
-        <v>9</v>
+        <v>2060</v>
       </c>
       <c r="D521" t="s">
-        <v>2060</v>
+        <v>2044</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>2061</v>
@@ -19081,10 +19105,10 @@
         <v>2063</v>
       </c>
       <c r="C522" t="s">
+        <v>9</v>
+      </c>
+      <c r="D522" t="s">
         <v>2064</v>
-      </c>
-      <c r="D522" t="s">
-        <v>2060</v>
       </c>
       <c r="E522" s="1" t="s">
         <v>2065</v>
@@ -19127,10 +19151,10 @@
         <v>2071</v>
       </c>
       <c r="C524" t="s">
-        <v>9</v>
+        <v>2072</v>
       </c>
       <c r="D524" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>2073</v>
@@ -19242,10 +19266,10 @@
         <v>2091</v>
       </c>
       <c r="C529" t="s">
+        <v>9</v>
+      </c>
+      <c r="D529" t="s">
         <v>2092</v>
-      </c>
-      <c r="D529" t="s">
-        <v>2088</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>2093</v>
@@ -19265,10 +19289,10 @@
         <v>2095</v>
       </c>
       <c r="C530" t="s">
+        <v>9</v>
+      </c>
+      <c r="D530" t="s">
         <v>2096</v>
-      </c>
-      <c r="D530" t="s">
-        <v>2088</v>
       </c>
       <c r="E530" s="1" t="s">
         <v>2097</v>
@@ -19288,10 +19312,10 @@
         <v>2099</v>
       </c>
       <c r="C531" t="s">
-        <v>9</v>
+        <v>2100</v>
       </c>
       <c r="D531" t="s">
-        <v>2100</v>
+        <v>2096</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>2101</v>
@@ -19311,10 +19335,10 @@
         <v>2103</v>
       </c>
       <c r="C532" t="s">
-        <v>9</v>
+        <v>2104</v>
       </c>
       <c r="D532" t="s">
-        <v>2104</v>
+        <v>2096</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>2105</v>
@@ -19357,7 +19381,13 @@
         <v>2111</v>
       </c>
       <c r="C534" t="s">
+        <v>9</v>
+      </c>
+      <c r="D534" t="s">
         <v>2112</v>
+      </c>
+      <c r="E534" s="1" t="s">
+        <v>2113</v>
       </c>
       <c r="F534" t="s">
         <v>12</v>
@@ -19368,88 +19398,82 @@
     </row>
     <row r="535" spans="1:7">
       <c r="A535" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="B535" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="C535" t="s">
-        <v>2115</v>
+        <v>9</v>
+      </c>
+      <c r="D535" t="s">
+        <v>2116</v>
       </c>
       <c r="E535" s="1" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="F535" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G535" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="536" spans="1:7">
       <c r="A536" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="B536" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="C536" t="s">
-        <v>2119</v>
-      </c>
-      <c r="D536" t="s">
         <v>2120</v>
       </c>
-      <c r="E536" s="1" t="s">
-        <v>2121</v>
-      </c>
       <c r="F536" t="s">
         <v>12</v>
       </c>
       <c r="G536" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:7">
       <c r="A537" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B537" t="s">
         <v>2122</v>
       </c>
-      <c r="B537" t="s">
+      <c r="C537" t="s">
         <v>2123</v>
       </c>
-      <c r="C537" t="s">
+      <c r="E537" s="1" t="s">
         <v>2124</v>
       </c>
-      <c r="D537" t="s">
-        <v>2120</v>
-      </c>
-      <c r="E537" s="1" t="s">
-        <v>2125</v>
-      </c>
       <c r="F537" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G537" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538" spans="1:7">
       <c r="A538" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B538" t="s">
         <v>2126</v>
       </c>
-      <c r="B538" t="s">
+      <c r="C538" t="s">
         <v>2127</v>
       </c>
-      <c r="C538" t="s">
+      <c r="D538" t="s">
         <v>2128</v>
-      </c>
-      <c r="D538" t="s">
-        <v>2120</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>2129</v>
       </c>
       <c r="F538" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G538" t="b">
         <v>1</v>
@@ -19465,6 +19489,9 @@
       <c r="C539" t="s">
         <v>2132</v>
       </c>
+      <c r="D539" t="s">
+        <v>2128</v>
+      </c>
       <c r="E539" s="1" t="s">
         <v>2133</v>
       </c>
@@ -19486,13 +19513,13 @@
         <v>2136</v>
       </c>
       <c r="D540" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
       <c r="E540" s="1" t="s">
         <v>2137</v>
       </c>
       <c r="F540" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G540" t="b">
         <v>1</v>
@@ -19508,11 +19535,8 @@
       <c r="C541" t="s">
         <v>2140</v>
       </c>
-      <c r="D541" t="s">
+      <c r="E541" s="1" t="s">
         <v>2141</v>
-      </c>
-      <c r="E541" s="1" t="s">
-        <v>2142</v>
       </c>
       <c r="F541" t="s">
         <v>12</v>
@@ -19523,39 +19547,39 @@
     </row>
     <row r="542" spans="1:7">
       <c r="A542" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B542" t="s">
         <v>2143</v>
       </c>
-      <c r="B542" t="s">
+      <c r="C542" t="s">
         <v>2144</v>
       </c>
-      <c r="C542" t="s">
+      <c r="D542" t="s">
+        <v>2128</v>
+      </c>
+      <c r="E542" s="1" t="s">
         <v>2145</v>
       </c>
-      <c r="D542" t="s">
-        <v>2120</v>
-      </c>
-      <c r="E542" s="1" t="s">
-        <v>2146</v>
-      </c>
       <c r="F542" t="s">
         <v>12</v>
       </c>
       <c r="G542" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543" spans="1:7">
       <c r="A543" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B543" t="s">
         <v>2147</v>
       </c>
-      <c r="B543" t="s">
+      <c r="C543" t="s">
         <v>2148</v>
       </c>
-      <c r="C543" t="s">
+      <c r="D543" t="s">
         <v>2149</v>
-      </c>
-      <c r="D543" t="s">
-        <v>2120</v>
       </c>
       <c r="E543" s="1" t="s">
         <v>2150</v>
@@ -19564,7 +19588,7 @@
         <v>12</v>
       </c>
       <c r="G543" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="544" spans="1:7">
@@ -19578,7 +19602,7 @@
         <v>2153</v>
       </c>
       <c r="D544" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>2154</v>
@@ -19587,7 +19611,7 @@
         <v>12</v>
       </c>
       <c r="G544" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545" spans="1:7">
@@ -19598,10 +19622,10 @@
         <v>2156</v>
       </c>
       <c r="C545" t="s">
-        <v>9</v>
+        <v>2157</v>
       </c>
       <c r="D545" t="s">
-        <v>2157</v>
+        <v>2128</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>2158</v>
@@ -19610,7 +19634,7 @@
         <v>12</v>
       </c>
       <c r="G545" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546" spans="1:7">
@@ -19623,6 +19647,9 @@
       <c r="C546" t="s">
         <v>2161</v>
       </c>
+      <c r="D546" t="s">
+        <v>2128</v>
+      </c>
       <c r="E546" s="1" t="s">
         <v>2162</v>
       </c>
@@ -19641,6 +19668,9 @@
         <v>2164</v>
       </c>
       <c r="C547" t="s">
+        <v>9</v>
+      </c>
+      <c r="D547" t="s">
         <v>2165</v>
       </c>
       <c r="E547" s="1" t="s">
@@ -19650,7 +19680,7 @@
         <v>12</v>
       </c>
       <c r="G547" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="548" spans="1:7">
@@ -19663,9 +19693,6 @@
       <c r="C548" t="s">
         <v>2169</v>
       </c>
-      <c r="D548" t="s">
-        <v>2120</v>
-      </c>
       <c r="E548" s="1" t="s">
         <v>2170</v>
       </c>
@@ -19686,54 +19713,51 @@
       <c r="C549" t="s">
         <v>2173</v>
       </c>
-      <c r="D549" t="s">
+      <c r="E549" s="1" t="s">
         <v>2174</v>
       </c>
-      <c r="E549" s="1" t="s">
-        <v>2175</v>
-      </c>
       <c r="F549" t="s">
         <v>12</v>
       </c>
       <c r="G549" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550" spans="1:7">
       <c r="A550" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B550" t="s">
         <v>2176</v>
       </c>
-      <c r="B550" t="s">
+      <c r="C550" t="s">
         <v>2177</v>
       </c>
-      <c r="C550" t="s">
-        <v>9</v>
-      </c>
       <c r="D550" t="s">
+        <v>2128</v>
+      </c>
+      <c r="E550" s="1" t="s">
         <v>2178</v>
       </c>
-      <c r="E550" s="1" t="s">
-        <v>2179</v>
-      </c>
       <c r="F550" t="s">
         <v>12</v>
       </c>
       <c r="G550" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551" spans="1:7">
       <c r="A551" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B551" t="s">
         <v>2180</v>
       </c>
-      <c r="B551" t="s">
+      <c r="C551" t="s">
         <v>2181</v>
       </c>
-      <c r="C551" t="s">
+      <c r="D551" t="s">
         <v>2182</v>
-      </c>
-      <c r="D551" t="s">
-        <v>2178</v>
       </c>
       <c r="E551" s="1" t="s">
         <v>2183</v>
@@ -19742,7 +19766,7 @@
         <v>12</v>
       </c>
       <c r="G551" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="552" spans="1:7">
@@ -19753,10 +19777,10 @@
         <v>2185</v>
       </c>
       <c r="C552" t="s">
+        <v>9</v>
+      </c>
+      <c r="D552" t="s">
         <v>2186</v>
-      </c>
-      <c r="D552" t="s">
-        <v>2178</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>2187</v>
@@ -19779,7 +19803,7 @@
         <v>2190</v>
       </c>
       <c r="D553" t="s">
-        <v>2178</v>
+        <v>2186</v>
       </c>
       <c r="E553" s="1" t="s">
         <v>2191</v>
@@ -19788,7 +19812,7 @@
         <v>12</v>
       </c>
       <c r="G553" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554" spans="1:7">
@@ -19799,10 +19823,10 @@
         <v>2193</v>
       </c>
       <c r="C554" t="s">
-        <v>9</v>
+        <v>2194</v>
       </c>
       <c r="D554" t="s">
-        <v>2194</v>
+        <v>2186</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>2195</v>
@@ -19825,10 +19849,10 @@
         <v>2198</v>
       </c>
       <c r="D555" t="s">
+        <v>2186</v>
+      </c>
+      <c r="E555" s="1" t="s">
         <v>2199</v>
-      </c>
-      <c r="E555" s="1" t="s">
-        <v>2200</v>
       </c>
       <c r="F555" t="s">
         <v>12</v>
@@ -19839,19 +19863,19 @@
     </row>
     <row r="556" spans="1:7">
       <c r="A556" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B556" t="s">
         <v>2201</v>
       </c>
-      <c r="B556" t="s">
+      <c r="C556" t="s">
+        <v>9</v>
+      </c>
+      <c r="D556" t="s">
         <v>2202</v>
       </c>
-      <c r="C556" t="s">
+      <c r="E556" s="1" t="s">
         <v>2203</v>
-      </c>
-      <c r="D556" t="s">
-        <v>2199</v>
-      </c>
-      <c r="E556" s="1" t="s">
-        <v>2204</v>
       </c>
       <c r="F556" t="s">
         <v>12</v>
@@ -19862,42 +19886,42 @@
     </row>
     <row r="557" spans="1:7">
       <c r="A557" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B557" t="s">
         <v>2205</v>
       </c>
-      <c r="B557" t="s">
+      <c r="C557" t="s">
         <v>2206</v>
       </c>
-      <c r="C557" t="s">
-        <v>9</v>
-      </c>
       <c r="D557" t="s">
-        <v>2199</v>
+        <v>2207</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="F557" t="s">
         <v>12</v>
       </c>
       <c r="G557" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558" spans="1:7">
       <c r="A558" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="B558" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="C558" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="D558" t="s">
-        <v>2199</v>
+        <v>2207</v>
       </c>
       <c r="E558" s="1" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="F558" t="s">
         <v>12</v>
@@ -19908,25 +19932,25 @@
     </row>
     <row r="559" spans="1:7">
       <c r="A559" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="B559" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="C559" t="s">
-        <v>2214</v>
+        <v>9</v>
       </c>
       <c r="D559" t="s">
-        <v>2199</v>
+        <v>2207</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>2215</v>
       </c>
       <c r="F559" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="G559" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="560" spans="1:7">
@@ -19937,10 +19961,10 @@
         <v>2217</v>
       </c>
       <c r="C560" t="s">
-        <v>9</v>
+        <v>2218</v>
       </c>
       <c r="D560" t="s">
-        <v>2218</v>
+        <v>2207</v>
       </c>
       <c r="E560" s="1" t="s">
         <v>2219</v>
@@ -19949,7 +19973,7 @@
         <v>12</v>
       </c>
       <c r="G560" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="561" spans="1:7">
@@ -19963,16 +19987,16 @@
         <v>2222</v>
       </c>
       <c r="D561" t="s">
-        <v>2218</v>
+        <v>2207</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>2223</v>
       </c>
       <c r="F561" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="G561" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="562" spans="1:7">
@@ -19983,10 +20007,10 @@
         <v>2225</v>
       </c>
       <c r="C562" t="s">
+        <v>9</v>
+      </c>
+      <c r="D562" t="s">
         <v>2226</v>
-      </c>
-      <c r="D562" t="s">
-        <v>2218</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>2227</v>
@@ -19995,7 +20019,7 @@
         <v>12</v>
       </c>
       <c r="G562" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="563" spans="1:7">
@@ -20009,7 +20033,7 @@
         <v>2230</v>
       </c>
       <c r="D563" t="s">
-        <v>2218</v>
+        <v>2226</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>2231</v>
@@ -20018,7 +20042,7 @@
         <v>12</v>
       </c>
       <c r="G563" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564" spans="1:7">
@@ -20029,10 +20053,10 @@
         <v>2233</v>
       </c>
       <c r="C564" t="s">
-        <v>9</v>
+        <v>2234</v>
       </c>
       <c r="D564" t="s">
-        <v>2234</v>
+        <v>2226</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>2235</v>
@@ -20041,7 +20065,7 @@
         <v>12</v>
       </c>
       <c r="G564" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="565" spans="1:7">
@@ -20055,7 +20079,10 @@
         <v>2238</v>
       </c>
       <c r="D565" t="s">
-        <v>2234</v>
+        <v>2226</v>
+      </c>
+      <c r="E565" s="1" t="s">
+        <v>2239</v>
       </c>
       <c r="F565" t="s">
         <v>12</v>
@@ -20066,47 +20093,90 @@
     </row>
     <row r="566" spans="1:7">
       <c r="A566" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="B566" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="C566" t="s">
-        <v>2241</v>
+        <v>9</v>
       </c>
       <c r="D566" t="s">
-        <v>2234</v>
+        <v>2242</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="F566" t="s">
         <v>12</v>
       </c>
       <c r="G566" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567" spans="1:7">
       <c r="A567" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="B567" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="C567" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="D567" t="s">
-        <v>2246</v>
-      </c>
-      <c r="E567" s="1" t="s">
+        <v>2242</v>
+      </c>
+      <c r="F567" t="s">
+        <v>12</v>
+      </c>
+      <c r="G567" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:7">
+      <c r="A568" t="s">
         <v>2247</v>
       </c>
-      <c r="F567" t="s">
-        <v>12</v>
-      </c>
-      <c r="G567" t="b">
+      <c r="B568" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C568" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D568" t="s">
+        <v>2242</v>
+      </c>
+      <c r="E568" s="1" t="s">
+        <v>2250</v>
+      </c>
+      <c r="F568" t="s">
+        <v>12</v>
+      </c>
+      <c r="G568" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:7">
+      <c r="A569" t="s">
+        <v>2251</v>
+      </c>
+      <c r="B569" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C569" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D569" t="s">
+        <v>2254</v>
+      </c>
+      <c r="E569" s="1" t="s">
+        <v>2255</v>
+      </c>
+      <c r="F569" t="s">
+        <v>12</v>
+      </c>
+      <c r="G569" t="b">
         <v>1</v>
       </c>
     </row>
@@ -20423,8 +20493,8 @@
     <hyperlink ref="E312" r:id="rId309"/>
     <hyperlink ref="E313" r:id="rId310"/>
     <hyperlink ref="E314" r:id="rId311"/>
-    <hyperlink ref="E316" r:id="rId312"/>
-    <hyperlink ref="E317" r:id="rId313"/>
+    <hyperlink ref="E315" r:id="rId312"/>
+    <hyperlink ref="E316" r:id="rId313"/>
     <hyperlink ref="E318" r:id="rId314"/>
     <hyperlink ref="E319" r:id="rId315"/>
     <hyperlink ref="E320" r:id="rId316"/>
@@ -20448,8 +20518,8 @@
     <hyperlink ref="E338" r:id="rId334"/>
     <hyperlink ref="E339" r:id="rId335"/>
     <hyperlink ref="E340" r:id="rId336"/>
-    <hyperlink ref="E342" r:id="rId337"/>
-    <hyperlink ref="E343" r:id="rId338"/>
+    <hyperlink ref="E341" r:id="rId337"/>
+    <hyperlink ref="E342" r:id="rId338"/>
     <hyperlink ref="E344" r:id="rId339"/>
     <hyperlink ref="E345" r:id="rId340"/>
     <hyperlink ref="E346" r:id="rId341"/>
@@ -20577,8 +20647,8 @@
     <hyperlink ref="E468" r:id="rId463"/>
     <hyperlink ref="E469" r:id="rId464"/>
     <hyperlink ref="E470" r:id="rId465"/>
-    <hyperlink ref="E472" r:id="rId466"/>
-    <hyperlink ref="E473" r:id="rId467"/>
+    <hyperlink ref="E471" r:id="rId466"/>
+    <hyperlink ref="E472" r:id="rId467"/>
     <hyperlink ref="E474" r:id="rId468"/>
     <hyperlink ref="E475" r:id="rId469"/>
     <hyperlink ref="E476" r:id="rId470"/>
@@ -20599,9 +20669,9 @@
     <hyperlink ref="E491" r:id="rId485"/>
     <hyperlink ref="E492" r:id="rId486"/>
     <hyperlink ref="E493" r:id="rId487"/>
-    <hyperlink ref="E494" r:id="rId488" location="/recherche-pm"/>
+    <hyperlink ref="E494" r:id="rId488"/>
     <hyperlink ref="E495" r:id="rId489"/>
-    <hyperlink ref="E496" r:id="rId490"/>
+    <hyperlink ref="E496" r:id="rId490" location="/recherche-pm"/>
     <hyperlink ref="E497" r:id="rId491"/>
     <hyperlink ref="E498" r:id="rId492"/>
     <hyperlink ref="E499" r:id="rId493"/>
@@ -20639,8 +20709,8 @@
     <hyperlink ref="E531" r:id="rId525"/>
     <hyperlink ref="E532" r:id="rId526"/>
     <hyperlink ref="E533" r:id="rId527"/>
-    <hyperlink ref="E535" r:id="rId528"/>
-    <hyperlink ref="E536" r:id="rId529"/>
+    <hyperlink ref="E534" r:id="rId528"/>
+    <hyperlink ref="E535" r:id="rId529"/>
     <hyperlink ref="E537" r:id="rId530"/>
     <hyperlink ref="E538" r:id="rId531"/>
     <hyperlink ref="E539" r:id="rId532"/>
@@ -20669,8 +20739,10 @@
     <hyperlink ref="E562" r:id="rId555"/>
     <hyperlink ref="E563" r:id="rId556"/>
     <hyperlink ref="E564" r:id="rId557"/>
-    <hyperlink ref="E566" r:id="rId558"/>
-    <hyperlink ref="E567" r:id="rId559"/>
+    <hyperlink ref="E565" r:id="rId558"/>
+    <hyperlink ref="E566" r:id="rId559"/>
+    <hyperlink ref="E568" r:id="rId560"/>
+    <hyperlink ref="E569" r:id="rId561"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
